--- a/data/cultural_property/data.xlsx
+++ b/data/cultural_property/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH184"/>
+  <dimension ref="A1:AH186"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1244,6 +1244,9 @@
       <c r="D9" t="str">
         <v>37201</v>
       </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
       <c r="F9" t="str">
         <v>香川県</v>
       </c>
@@ -1253,18 +1256,48 @@
       <c r="H9" t="str">
         <v>瀬戸内海歴史民俗資料館</v>
       </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
       <c r="L9" t="str">
         <v>国指定重要文化財</v>
       </c>
       <c r="M9" t="str">
         <v>建造物</v>
       </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
       <c r="O9" t="str">
         <v>高松市亀水町1412-2</v>
       </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
       <c r="Q9" t="str">
         <v>087-881-4707</v>
       </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
       <c r="W9" t="str">
         <v>2024-12-09</v>
       </c>
@@ -1279,6 +1312,24 @@
       </c>
       <c r="AA9" t="str">
         <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始。</v>
+      </c>
+      <c r="AB9" t="str">
+        <v/>
+      </c>
+      <c r="AC9" t="str">
+        <v/>
+      </c>
+      <c r="AD9" t="str">
+        <v/>
+      </c>
+      <c r="AE9" t="str">
+        <v/>
+      </c>
+      <c r="AF9" t="str">
+        <v/>
+      </c>
+      <c r="AG9" t="str">
+        <v/>
       </c>
       <c r="AH9" t="str">
         <v>https://www.pref.kagawa.lg.jp/setorekishi/index.html</v>
@@ -1297,6 +1348,9 @@
       <c r="D10" t="str">
         <v>37201</v>
       </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
       <c r="F10" t="str">
         <v>香川県</v>
       </c>
@@ -1306,17 +1360,83 @@
       <c r="H10" t="str">
         <v>男木島灯台（灯台、旧吏員退息所、旧第一物置）</v>
       </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
       <c r="L10" t="str">
         <v>国指定重要文化財</v>
       </c>
       <c r="M10" t="str">
         <v>建造物</v>
       </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
       <c r="O10" t="str">
         <v>高松市男木町字洲鼻1062</v>
       </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
       <c r="W10" t="str">
         <v>2026-01-15</v>
+      </c>
+      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+      <c r="AA10" t="str">
+        <v/>
+      </c>
+      <c r="AB10" t="str">
+        <v/>
+      </c>
+      <c r="AC10" t="str">
+        <v/>
+      </c>
+      <c r="AD10" t="str">
+        <v/>
+      </c>
+      <c r="AE10" t="str">
+        <v/>
+      </c>
+      <c r="AF10" t="str">
+        <v/>
+      </c>
+      <c r="AG10" t="str">
+        <v/>
+      </c>
+      <c r="AH10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1332,6 +1452,9 @@
       <c r="D11" t="str">
         <v>37201</v>
       </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
       <c r="F11" t="str">
         <v>香川県</v>
       </c>
@@ -1341,6 +1464,15 @@
       <c r="H11" t="str">
         <v>香川県庁舎旧本館及び東館</v>
       </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
       <c r="L11" t="str">
         <v>国指定重要文化財</v>
       </c>
@@ -1353,8 +1485,62 @@
       <c r="O11" t="str">
         <v>高松市番町四丁目1-3</v>
       </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
       <c r="W11" t="str">
         <v>2022-02-09</v>
+      </c>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="str">
+        <v/>
+      </c>
+      <c r="AA11" t="str">
+        <v/>
+      </c>
+      <c r="AB11" t="str">
+        <v/>
+      </c>
+      <c r="AC11" t="str">
+        <v/>
+      </c>
+      <c r="AD11" t="str">
+        <v/>
+      </c>
+      <c r="AE11" t="str">
+        <v/>
+      </c>
+      <c r="AF11" t="str">
+        <v/>
+      </c>
+      <c r="AG11" t="str">
+        <v/>
+      </c>
+      <c r="AH11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -3242,6 +3428,9 @@
       <c r="D30" t="str">
         <v>37201</v>
       </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
       <c r="F30" t="str">
         <v>香川県</v>
       </c>
@@ -3251,17 +3440,83 @@
       <c r="H30" t="str">
         <v>刀　折返銘　備州長船景光</v>
       </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
       <c r="L30" t="str">
         <v>国指定重要文化財</v>
       </c>
       <c r="M30" t="str">
         <v>工芸品</v>
       </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
       <c r="O30" t="str">
         <v>高松市香西西町</v>
       </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+      <c r="U30" t="str">
+        <v/>
+      </c>
+      <c r="V30" t="str">
+        <v/>
+      </c>
       <c r="W30" t="str">
         <v>1954-03-20</v>
+      </c>
+      <c r="X30" t="str">
+        <v/>
+      </c>
+      <c r="Y30" t="str">
+        <v/>
+      </c>
+      <c r="Z30" t="str">
+        <v/>
+      </c>
+      <c r="AA30" t="str">
+        <v/>
+      </c>
+      <c r="AB30" t="str">
+        <v/>
+      </c>
+      <c r="AC30" t="str">
+        <v/>
+      </c>
+      <c r="AD30" t="str">
+        <v/>
+      </c>
+      <c r="AE30" t="str">
+        <v/>
+      </c>
+      <c r="AF30" t="str">
+        <v/>
+      </c>
+      <c r="AG30" t="str">
+        <v/>
+      </c>
+      <c r="AH30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -3901,6 +4156,9 @@
       <c r="D37" t="str">
         <v>37201</v>
       </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
       <c r="F37" t="str">
         <v>香川県</v>
       </c>
@@ -3910,6 +4168,15 @@
       <c r="H37" t="str">
         <v>古今和歌集巻下（片仮名本）</v>
       </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
       <c r="L37" t="str">
         <v>国指定重要文化財</v>
       </c>
@@ -3922,8 +4189,62 @@
       <c r="O37" t="str">
         <v>京都府京都市上京区寺町通荒神口下る松陰町138-1</v>
       </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+      <c r="R37" t="str">
+        <v/>
+      </c>
+      <c r="S37" t="str">
+        <v/>
+      </c>
+      <c r="T37" t="str">
+        <v/>
+      </c>
+      <c r="U37" t="str">
+        <v/>
+      </c>
+      <c r="V37" t="str">
+        <v/>
+      </c>
       <c r="W37" t="str">
         <v>2016-08-29</v>
+      </c>
+      <c r="X37" t="str">
+        <v/>
+      </c>
+      <c r="Y37" t="str">
+        <v/>
+      </c>
+      <c r="Z37" t="str">
+        <v/>
+      </c>
+      <c r="AA37" t="str">
+        <v/>
+      </c>
+      <c r="AB37" t="str">
+        <v/>
+      </c>
+      <c r="AC37" t="str">
+        <v/>
+      </c>
+      <c r="AD37" t="str">
+        <v/>
+      </c>
+      <c r="AE37" t="str">
+        <v/>
+      </c>
+      <c r="AF37" t="str">
+        <v/>
+      </c>
+      <c r="AG37" t="str">
+        <v/>
+      </c>
+      <c r="AH37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -5603,6 +5924,9 @@
       <c r="D54" t="str">
         <v>37201</v>
       </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
       <c r="F54" t="str">
         <v>香川県</v>
       </c>
@@ -5612,17 +5936,83 @@
       <c r="H54" t="str">
         <v>勝賀城跡</v>
       </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
       <c r="L54" t="str">
         <v>国指定記念物</v>
       </c>
       <c r="M54" t="str">
         <v>史跡</v>
       </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
       <c r="O54" t="str">
         <v>高松市鬼無町佐料、鬼無町是竹、中山町、香西西町、植松町</v>
       </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
+        <v/>
+      </c>
+      <c r="T54" t="str">
+        <v/>
+      </c>
+      <c r="U54" t="str">
+        <v/>
+      </c>
+      <c r="V54" t="str">
+        <v/>
+      </c>
       <c r="W54" t="str">
         <v>2024-02-21</v>
+      </c>
+      <c r="X54" t="str">
+        <v/>
+      </c>
+      <c r="Y54" t="str">
+        <v/>
+      </c>
+      <c r="Z54" t="str">
+        <v/>
+      </c>
+      <c r="AA54" t="str">
+        <v/>
+      </c>
+      <c r="AB54" t="str">
+        <v/>
+      </c>
+      <c r="AC54" t="str">
+        <v/>
+      </c>
+      <c r="AD54" t="str">
+        <v/>
+      </c>
+      <c r="AE54" t="str">
+        <v/>
+      </c>
+      <c r="AF54" t="str">
+        <v/>
+      </c>
+      <c r="AG54" t="str">
+        <v/>
+      </c>
+      <c r="AH54" t="str">
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -5638,6 +6028,9 @@
       <c r="D55" t="str">
         <v>37201</v>
       </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
       <c r="F55" t="str">
         <v>香川県</v>
       </c>
@@ -5647,6 +6040,15 @@
       <c r="H55" t="str">
         <v>高松藩主松平家墓所</v>
       </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
       <c r="L55" t="str">
         <v>国指定記念物</v>
       </c>
@@ -5659,14 +6061,62 @@
       <c r="O55" t="str">
         <v>高松市仏生山町</v>
       </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
       <c r="Q55" t="str">
         <v>087-889-0406</v>
       </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
+        <v/>
+      </c>
+      <c r="T55" t="str">
+        <v/>
+      </c>
+      <c r="U55" t="str">
+        <v/>
+      </c>
+      <c r="V55" t="str">
+        <v/>
+      </c>
       <c r="W55" t="str">
         <v>2019-02-26</v>
       </c>
+      <c r="X55" t="str">
+        <v/>
+      </c>
+      <c r="Y55" t="str">
+        <v/>
+      </c>
+      <c r="Z55" t="str">
+        <v/>
+      </c>
       <c r="AA55" t="str">
         <v>【公開日】歴代藩主命日（4月12日、10月20日、9月16日、7月18日、3月10日、7月28日、8月25日、10月17日）</v>
+      </c>
+      <c r="AB55" t="str">
+        <v/>
+      </c>
+      <c r="AC55" t="str">
+        <v/>
+      </c>
+      <c r="AD55" t="str">
+        <v/>
+      </c>
+      <c r="AE55" t="str">
+        <v/>
+      </c>
+      <c r="AF55" t="str">
+        <v/>
+      </c>
+      <c r="AG55" t="str">
+        <v/>
+      </c>
+      <c r="AH55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -6618,6 +7068,9 @@
       <c r="D65" t="str">
         <v>37201</v>
       </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
       <c r="F65" t="str">
         <v>香川県</v>
       </c>
@@ -6627,6 +7080,15 @@
       <c r="H65" t="str">
         <v>渡舟　小林萬吾筆</v>
       </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
       <c r="L65" t="str">
         <v>県指定有形文化財</v>
       </c>
@@ -6639,9 +7101,27 @@
       <c r="O65" t="str">
         <v>高松市玉藻町5-5</v>
       </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
       <c r="Q65" t="str">
         <v>087-822-0002</v>
       </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
+        <v/>
+      </c>
+      <c r="T65" t="str">
+        <v/>
+      </c>
+      <c r="U65" t="str">
+        <v/>
+      </c>
+      <c r="V65" t="str">
+        <v/>
+      </c>
       <c r="W65" t="str">
         <v>2025-08-29</v>
       </c>
@@ -6656,6 +7136,24 @@
       </c>
       <c r="AA65" t="str">
         <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
+      </c>
+      <c r="AB65" t="str">
+        <v/>
+      </c>
+      <c r="AC65" t="str">
+        <v/>
+      </c>
+      <c r="AD65" t="str">
+        <v/>
+      </c>
+      <c r="AE65" t="str">
+        <v/>
+      </c>
+      <c r="AF65" t="str">
+        <v/>
+      </c>
+      <c r="AG65" t="str">
+        <v/>
       </c>
       <c r="AH65" t="str">
         <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
@@ -7194,6 +7692,9 @@
       <c r="D71" t="str">
         <v>37201</v>
       </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
       <c r="F71" t="str">
         <v>香川県</v>
       </c>
@@ -7203,6 +7704,15 @@
       <c r="H71" t="str">
         <v>木造六字明王立像</v>
       </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
       <c r="L71" t="str">
         <v>県指定有形文化財</v>
       </c>
@@ -7215,8 +7725,62 @@
       <c r="O71" t="str">
         <v>高松市多肥上町887-2</v>
       </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v/>
+      </c>
+      <c r="T71" t="str">
+        <v/>
+      </c>
+      <c r="U71" t="str">
+        <v/>
+      </c>
+      <c r="V71" t="str">
+        <v/>
+      </c>
       <c r="W71" t="str">
         <v>2021-03-30</v>
+      </c>
+      <c r="X71" t="str">
+        <v/>
+      </c>
+      <c r="Y71" t="str">
+        <v/>
+      </c>
+      <c r="Z71" t="str">
+        <v/>
+      </c>
+      <c r="AA71" t="str">
+        <v/>
+      </c>
+      <c r="AB71" t="str">
+        <v/>
+      </c>
+      <c r="AC71" t="str">
+        <v/>
+      </c>
+      <c r="AD71" t="str">
+        <v/>
+      </c>
+      <c r="AE71" t="str">
+        <v/>
+      </c>
+      <c r="AF71" t="str">
+        <v/>
+      </c>
+      <c r="AG71" t="str">
+        <v/>
+      </c>
+      <c r="AH71" t="str">
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -7648,6 +8212,9 @@
       <c r="D76" t="str">
         <v>37201</v>
       </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
       <c r="F76" t="str">
         <v>香川県</v>
       </c>
@@ -7657,6 +8224,15 @@
       <c r="H76" t="str">
         <v>蒟醤料紙箱及び硯箱　玉楮象谷作　附 硯箱付属文具</v>
       </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
       <c r="L76" t="str">
         <v>県指定有形文化財</v>
       </c>
@@ -7669,9 +8245,27 @@
       <c r="O76" t="str">
         <v>高松市玉藻町5-5</v>
       </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
       <c r="Q76" t="str">
         <v>087-822-0002</v>
       </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
+      <c r="T76" t="str">
+        <v/>
+      </c>
+      <c r="U76" t="str">
+        <v/>
+      </c>
+      <c r="V76" t="str">
+        <v/>
+      </c>
       <c r="W76" t="str">
         <v>2020-09-13</v>
       </c>
@@ -7686,6 +8280,24 @@
       </c>
       <c r="AA76" t="str">
         <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
+      </c>
+      <c r="AB76" t="str">
+        <v/>
+      </c>
+      <c r="AC76" t="str">
+        <v/>
+      </c>
+      <c r="AD76" t="str">
+        <v/>
+      </c>
+      <c r="AE76" t="str">
+        <v/>
+      </c>
+      <c r="AF76" t="str">
+        <v/>
+      </c>
+      <c r="AG76" t="str">
+        <v/>
       </c>
       <c r="AH76" t="str">
         <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
@@ -7704,6 +8316,9 @@
       <c r="D77" t="str">
         <v>37201</v>
       </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
       <c r="F77" t="str">
         <v>香川県</v>
       </c>
@@ -7713,6 +8328,15 @@
       <c r="H77" t="str">
         <v>堆朱鼓箱　玉楮象谷作　狩野永笑図</v>
       </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
       <c r="L77" t="str">
         <v>県指定有形文化財</v>
       </c>
@@ -7725,9 +8349,27 @@
       <c r="O77" t="str">
         <v>高松市玉藻町5-5</v>
       </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
       <c r="Q77" t="str">
         <v>087-822-0002</v>
       </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
+      <c r="S77" t="str">
+        <v/>
+      </c>
+      <c r="T77" t="str">
+        <v/>
+      </c>
+      <c r="U77" t="str">
+        <v/>
+      </c>
+      <c r="V77" t="str">
+        <v/>
+      </c>
       <c r="W77" t="str">
         <v>2020-09-13</v>
       </c>
@@ -7742,6 +8384,24 @@
       </c>
       <c r="AA77" t="str">
         <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
+      </c>
+      <c r="AB77" t="str">
+        <v/>
+      </c>
+      <c r="AC77" t="str">
+        <v/>
+      </c>
+      <c r="AD77" t="str">
+        <v/>
+      </c>
+      <c r="AE77" t="str">
+        <v/>
+      </c>
+      <c r="AF77" t="str">
+        <v/>
+      </c>
+      <c r="AG77" t="str">
+        <v/>
       </c>
       <c r="AH77" t="str">
         <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
@@ -7760,9 +8420,6 @@
       <c r="D78" t="str">
         <v>37201</v>
       </c>
-      <c r="E78" t="str">
-        <v/>
-      </c>
       <c r="F78" t="str">
         <v>香川県</v>
       </c>
@@ -7770,22 +8427,13 @@
         <v>高松市</v>
       </c>
       <c r="H78" t="str">
-        <v>平形銅剣   高瀬町北条出土</v>
-      </c>
-      <c r="I78" t="str">
-        <v/>
-      </c>
-      <c r="J78" t="str">
-        <v/>
-      </c>
-      <c r="K78" t="str">
-        <v/>
+        <v>堆黒松ケ浦香合　玉楮象谷作</v>
       </c>
       <c r="L78" t="str">
         <v>県指定有形文化財</v>
       </c>
       <c r="M78" t="str">
-        <v>考古資料</v>
+        <v>工芸品</v>
       </c>
       <c r="N78" t="str">
         <v>香川県立ミュージアム</v>
@@ -7793,29 +8441,11 @@
       <c r="O78" t="str">
         <v>高松市玉藻町5-5</v>
       </c>
-      <c r="P78" t="str">
-        <v/>
-      </c>
       <c r="Q78" t="str">
         <v>087-822-0002</v>
       </c>
-      <c r="R78" t="str">
-        <v/>
-      </c>
-      <c r="S78" t="str">
-        <v/>
-      </c>
-      <c r="T78" t="str">
-        <v/>
-      </c>
-      <c r="U78" t="str">
-        <v/>
-      </c>
-      <c r="V78" t="str">
-        <v/>
-      </c>
       <c r="W78" t="str">
-        <v>1978-12-26</v>
+        <v>2026-03-31</v>
       </c>
       <c r="X78" t="str">
         <v>火水木金土日</v>
@@ -7828,24 +8458,6 @@
       </c>
       <c r="AA78" t="str">
         <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
-      </c>
-      <c r="AB78" t="str">
-        <v/>
-      </c>
-      <c r="AC78" t="str">
-        <v/>
-      </c>
-      <c r="AD78" t="str">
-        <v/>
-      </c>
-      <c r="AE78" t="str">
-        <v/>
-      </c>
-      <c r="AF78" t="str">
-        <v/>
-      </c>
-      <c r="AG78" t="str">
-        <v/>
       </c>
       <c r="AH78" t="str">
         <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
@@ -7856,17 +8468,14 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>0</v>
+        <v>34.34997</v>
       </c>
       <c r="C79" t="str">
-        <v>0</v>
+        <v>134.053336</v>
       </c>
       <c r="D79" t="str">
         <v>37201</v>
       </c>
-      <c r="E79" t="str">
-        <v/>
-      </c>
       <c r="F79" t="str">
         <v>香川県</v>
       </c>
@@ -7874,85 +8483,40 @@
         <v>高松市</v>
       </c>
       <c r="H79" t="str">
-        <v>蒟醤</v>
-      </c>
-      <c r="I79" t="str">
-        <v/>
-      </c>
-      <c r="J79" t="str">
-        <v/>
-      </c>
-      <c r="K79" t="str">
-        <v/>
+        <v>一角印籠　玉楮象谷作　 附　木製箱 　 天保十年己亥仲秋玉楮正直謹製墨書</v>
       </c>
       <c r="L79" t="str">
-        <v>県指定無形文化財</v>
+        <v>県指定有形文化財</v>
       </c>
       <c r="M79" t="str">
-        <v>工芸技術</v>
+        <v>工芸品</v>
       </c>
       <c r="N79" t="str">
-        <v/>
+        <v>香川県立ミュージアム</v>
       </c>
       <c r="O79" t="str">
-        <v/>
-      </c>
-      <c r="P79" t="str">
-        <v/>
+        <v>高松市玉藻町5-5</v>
       </c>
       <c r="Q79" t="str">
-        <v/>
-      </c>
-      <c r="R79" t="str">
-        <v/>
-      </c>
-      <c r="S79" t="str">
-        <v/>
-      </c>
-      <c r="T79" t="str">
-        <v/>
-      </c>
-      <c r="U79" t="str">
-        <v/>
-      </c>
-      <c r="V79" t="str">
-        <v>伊賀　寛泰、太田　勝子</v>
+        <v>087-822-0002</v>
       </c>
       <c r="W79" t="str">
-        <v>2001-03-27、2001-03-27</v>
+        <v>2026-03-31</v>
       </c>
       <c r="X79" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y79" t="str">
-        <v/>
+        <v>09:00</v>
       </c>
       <c r="Z79" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA79" t="str">
-        <v/>
-      </c>
-      <c r="AB79" t="str">
-        <v/>
-      </c>
-      <c r="AC79" t="str">
-        <v/>
-      </c>
-      <c r="AD79" t="str">
-        <v/>
-      </c>
-      <c r="AE79" t="str">
-        <v/>
-      </c>
-      <c r="AF79" t="str">
-        <v/>
-      </c>
-      <c r="AG79" t="str">
-        <v/>
+        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
       </c>
       <c r="AH79" t="str">
-        <v/>
+        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
       </c>
     </row>
     <row r="80">
@@ -7960,10 +8524,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>0</v>
+        <v>34.34997</v>
       </c>
       <c r="C80" t="str">
-        <v>0</v>
+        <v>134.053336</v>
       </c>
       <c r="D80" t="str">
         <v>37201</v>
@@ -7978,7 +8542,7 @@
         <v>高松市</v>
       </c>
       <c r="H80" t="str">
-        <v>彫漆</v>
+        <v>平形銅剣   高瀬町北条出土</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -7990,22 +8554,22 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>県指定無形文化財</v>
+        <v>県指定有形文化財</v>
       </c>
       <c r="M80" t="str">
-        <v>工芸技術</v>
+        <v>考古資料</v>
       </c>
       <c r="N80" t="str">
-        <v/>
+        <v>香川県立ミュージアム</v>
       </c>
       <c r="O80" t="str">
-        <v/>
+        <v>高松市玉藻町5-5</v>
       </c>
       <c r="P80" t="str">
         <v/>
       </c>
       <c r="Q80" t="str">
-        <v/>
+        <v>087-822-0002</v>
       </c>
       <c r="R80" t="str">
         <v/>
@@ -8020,22 +8584,22 @@
         <v/>
       </c>
       <c r="V80" t="str">
-        <v>北岡　省三</v>
+        <v/>
       </c>
       <c r="W80" t="str">
-        <v>2001-03-27</v>
+        <v>1978-12-26</v>
       </c>
       <c r="X80" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y80" t="str">
-        <v/>
+        <v>09:00</v>
       </c>
       <c r="Z80" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA80" t="str">
-        <v/>
+        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
       </c>
       <c r="AB80" t="str">
         <v/>
@@ -8056,7 +8620,7 @@
         <v/>
       </c>
       <c r="AH80" t="str">
-        <v/>
+        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
       </c>
     </row>
     <row r="81">
@@ -8082,7 +8646,7 @@
         <v>高松市</v>
       </c>
       <c r="H81" t="str">
-        <v>きゅう漆</v>
+        <v>蒟醤</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -8124,10 +8688,10 @@
         <v/>
       </c>
       <c r="V81" t="str">
-        <v>竹内　幸司</v>
+        <v>伊賀　寛泰、太田　勝子</v>
       </c>
       <c r="W81" t="str">
-        <v>2009-03-31</v>
+        <v>2001-03-27、2001-03-27</v>
       </c>
       <c r="X81" t="str">
         <v/>
@@ -8186,7 +8750,7 @@
         <v>高松市</v>
       </c>
       <c r="H82" t="str">
-        <v>香翠座人形頭</v>
+        <v>彫漆</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -8198,22 +8762,22 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>県指定民俗文化財</v>
+        <v>県指定無形文化財</v>
       </c>
       <c r="M82" t="str">
-        <v>有形民俗</v>
+        <v>工芸技術</v>
       </c>
       <c r="N82" t="str">
-        <v>円座コミュニティセンター</v>
+        <v/>
       </c>
       <c r="O82" t="str">
-        <v>高松市円座町1622-1</v>
+        <v/>
       </c>
       <c r="P82" t="str">
         <v/>
       </c>
       <c r="Q82" t="str">
-        <v>087-886-4993</v>
+        <v/>
       </c>
       <c r="R82" t="str">
         <v/>
@@ -8228,10 +8792,10 @@
         <v/>
       </c>
       <c r="V82" t="str">
-        <v/>
+        <v>北岡　省三</v>
       </c>
       <c r="W82" t="str">
-        <v>1962-09-20</v>
+        <v>2001-03-27</v>
       </c>
       <c r="X82" t="str">
         <v/>
@@ -8290,7 +8854,7 @@
         <v>高松市</v>
       </c>
       <c r="H83" t="str">
-        <v>ひょうげ祭りの神具</v>
+        <v>きゅう漆</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -8302,16 +8866,16 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>県指定民俗文化財</v>
+        <v>県指定無形文化財</v>
       </c>
       <c r="M83" t="str">
-        <v>有形民俗</v>
+        <v>工芸技術</v>
       </c>
       <c r="N83" t="str">
         <v/>
       </c>
       <c r="O83" t="str">
-        <v>高松市香川町浅野</v>
+        <v/>
       </c>
       <c r="P83" t="str">
         <v/>
@@ -8332,10 +8896,10 @@
         <v/>
       </c>
       <c r="V83" t="str">
-        <v/>
+        <v>竹内　幸司</v>
       </c>
       <c r="W83" t="str">
-        <v>1965-04-03</v>
+        <v>2009-03-31</v>
       </c>
       <c r="X83" t="str">
         <v/>
@@ -8394,7 +8958,7 @@
         <v>高松市</v>
       </c>
       <c r="H84" t="str">
-        <v>冠纓神社の大獅子　（二頭）</v>
+        <v>香翠座人形頭</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -8412,16 +8976,16 @@
         <v>有形民俗</v>
       </c>
       <c r="N84" t="str">
-        <v>冠櫻神社ほか</v>
+        <v>円座コミュニティセンター</v>
       </c>
       <c r="O84" t="str">
-        <v>高松市香南町由佐、高松市香南町池内</v>
+        <v>高松市円座町1622-1</v>
       </c>
       <c r="P84" t="str">
         <v/>
       </c>
       <c r="Q84" t="str">
-        <v/>
+        <v>087-886-4993</v>
       </c>
       <c r="R84" t="str">
         <v/>
@@ -8439,7 +9003,7 @@
         <v/>
       </c>
       <c r="W84" t="str">
-        <v>1970-04-28</v>
+        <v>1962-09-20</v>
       </c>
       <c r="X84" t="str">
         <v/>
@@ -8480,10 +9044,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>34.34997</v>
+        <v>0</v>
       </c>
       <c r="C85" t="str">
-        <v>134.053336</v>
+        <v>0</v>
       </c>
       <c r="D85" t="str">
         <v>37201</v>
@@ -8498,7 +9062,7 @@
         <v>高松市</v>
       </c>
       <c r="H85" t="str">
-        <v>高松藩飛竜丸船明細切絵図</v>
+        <v>ひょうげ祭りの神具</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -8516,16 +9080,16 @@
         <v>有形民俗</v>
       </c>
       <c r="N85" t="str">
-        <v>香川県立ミュージアム</v>
+        <v/>
       </c>
       <c r="O85" t="str">
-        <v>高松市玉藻町5-5</v>
+        <v>高松市香川町浅野</v>
       </c>
       <c r="P85" t="str">
         <v/>
       </c>
       <c r="Q85" t="str">
-        <v>087-822-0002</v>
+        <v/>
       </c>
       <c r="R85" t="str">
         <v/>
@@ -8543,19 +9107,19 @@
         <v/>
       </c>
       <c r="W85" t="str">
-        <v>1977-07-26</v>
+        <v>1965-04-03</v>
       </c>
       <c r="X85" t="str">
-        <v>火水木金土日</v>
+        <v/>
       </c>
       <c r="Y85" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="Z85" t="str">
-        <v>17:00</v>
+        <v/>
       </c>
       <c r="AA85" t="str">
-        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
+        <v/>
       </c>
       <c r="AB85" t="str">
         <v/>
@@ -8576,7 +9140,7 @@
         <v/>
       </c>
       <c r="AH85" t="str">
-        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -8602,7 +9166,7 @@
         <v>高松市</v>
       </c>
       <c r="H86" t="str">
-        <v>粟島伊勢神宮奉納舟絵馬</v>
+        <v>冠纓神社の大獅子　（二頭）</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -8620,16 +9184,16 @@
         <v>有形民俗</v>
       </c>
       <c r="N86" t="str">
-        <v>瀬戸内海歴史民俗資料館ほか</v>
+        <v>冠櫻神社ほか</v>
       </c>
       <c r="O86" t="str">
-        <v>高松市亀水町</v>
+        <v>高松市香南町由佐、高松市香南町池内</v>
       </c>
       <c r="P86" t="str">
         <v/>
       </c>
       <c r="Q86" t="str">
-        <v>087-881-4707</v>
+        <v/>
       </c>
       <c r="R86" t="str">
         <v/>
@@ -8647,19 +9211,19 @@
         <v/>
       </c>
       <c r="W86" t="str">
-        <v>1977-07-26</v>
+        <v>1970-04-28</v>
       </c>
       <c r="X86" t="str">
-        <v>火水木金土日</v>
+        <v/>
       </c>
       <c r="Y86" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="Z86" t="str">
-        <v>17:00</v>
+        <v/>
       </c>
       <c r="AA86" t="str">
-        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始。</v>
+        <v/>
       </c>
       <c r="AB86" t="str">
         <v/>
@@ -8680,7 +9244,7 @@
         <v/>
       </c>
       <c r="AH86" t="str">
-        <v>https://www.pref.kagawa.lg.jp/setorekishi/index.html</v>
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -8688,10 +9252,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>0</v>
+        <v>34.34997</v>
       </c>
       <c r="C87" t="str">
-        <v>0</v>
+        <v>134.053336</v>
       </c>
       <c r="D87" t="str">
         <v>37201</v>
@@ -8706,7 +9270,7 @@
         <v>高松市</v>
       </c>
       <c r="H87" t="str">
-        <v>祇園座</v>
+        <v>高松藩飛竜丸船明細切絵図</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -8721,19 +9285,19 @@
         <v>県指定民俗文化財</v>
       </c>
       <c r="M87" t="str">
-        <v>無形民俗</v>
+        <v>有形民俗</v>
       </c>
       <c r="N87" t="str">
-        <v/>
+        <v>香川県立ミュージアム</v>
       </c>
       <c r="O87" t="str">
-        <v>高松市香川町東谷</v>
+        <v>高松市玉藻町5-5</v>
       </c>
       <c r="P87" t="str">
         <v/>
       </c>
       <c r="Q87" t="str">
-        <v/>
+        <v>087-822-0002</v>
       </c>
       <c r="R87" t="str">
         <v/>
@@ -8751,19 +9315,19 @@
         <v/>
       </c>
       <c r="W87" t="str">
-        <v>1965-04-03</v>
+        <v>1977-07-26</v>
       </c>
       <c r="X87" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y87" t="str">
-        <v/>
+        <v>09:00</v>
       </c>
       <c r="Z87" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA87" t="str">
-        <v/>
+        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
       </c>
       <c r="AB87" t="str">
         <v/>
@@ -8784,7 +9348,7 @@
         <v/>
       </c>
       <c r="AH87" t="str">
-        <v/>
+        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
       </c>
     </row>
     <row r="88">
@@ -8810,7 +9374,7 @@
         <v>高松市</v>
       </c>
       <c r="H88" t="str">
-        <v>庵治締太鼓</v>
+        <v>粟島伊勢神宮奉納舟絵馬</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -8825,19 +9389,19 @@
         <v>県指定民俗文化財</v>
       </c>
       <c r="M88" t="str">
-        <v>無形民俗</v>
+        <v>有形民俗</v>
       </c>
       <c r="N88" t="str">
-        <v/>
+        <v>瀬戸内海歴史民俗資料館ほか</v>
       </c>
       <c r="O88" t="str">
-        <v>高松市庵治町丸山</v>
+        <v>高松市亀水町</v>
       </c>
       <c r="P88" t="str">
         <v/>
       </c>
       <c r="Q88" t="str">
-        <v/>
+        <v>087-881-4707</v>
       </c>
       <c r="R88" t="str">
         <v/>
@@ -8855,19 +9419,19 @@
         <v/>
       </c>
       <c r="W88" t="str">
-        <v>1978-12-26</v>
+        <v>1977-07-26</v>
       </c>
       <c r="X88" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y88" t="str">
-        <v/>
+        <v>09:00</v>
       </c>
       <c r="Z88" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA88" t="str">
-        <v/>
+        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始。</v>
       </c>
       <c r="AB88" t="str">
         <v/>
@@ -8888,7 +9452,7 @@
         <v/>
       </c>
       <c r="AH88" t="str">
-        <v/>
+        <v>https://www.pref.kagawa.lg.jp/setorekishi/index.html</v>
       </c>
     </row>
     <row r="89">
@@ -8914,7 +9478,7 @@
         <v>高松市</v>
       </c>
       <c r="H89" t="str">
-        <v>香翠座デコ芝居</v>
+        <v>祇園座</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -8935,7 +9499,7 @@
         <v/>
       </c>
       <c r="O89" t="str">
-        <v>高松市円座町</v>
+        <v>高松市香川町東谷</v>
       </c>
       <c r="P89" t="str">
         <v/>
@@ -8959,7 +9523,7 @@
         <v/>
       </c>
       <c r="W89" t="str">
-        <v>2004-03-05</v>
+        <v>1965-04-03</v>
       </c>
       <c r="X89" t="str">
         <v/>
@@ -9018,7 +9582,7 @@
         <v>高松市</v>
       </c>
       <c r="H90" t="str">
-        <v>庵治の船祭り</v>
+        <v>庵治締太鼓</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -9039,7 +9603,7 @@
         <v/>
       </c>
       <c r="O90" t="str">
-        <v>高松市庵治町才田</v>
+        <v>高松市庵治町丸山</v>
       </c>
       <c r="P90" t="str">
         <v/>
@@ -9063,7 +9627,7 @@
         <v/>
       </c>
       <c r="W90" t="str">
-        <v>2009-06-26</v>
+        <v>1978-12-26</v>
       </c>
       <c r="X90" t="str">
         <v/>
@@ -9122,7 +9686,7 @@
         <v>高松市</v>
       </c>
       <c r="H91" t="str">
-        <v>生駒親正夫妻墓所</v>
+        <v>香翠座デコ芝居</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -9134,16 +9698,16 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>県指定記念物</v>
+        <v>県指定民俗文化財</v>
       </c>
       <c r="M91" t="str">
-        <v>史跡</v>
+        <v>無形民俗</v>
       </c>
       <c r="N91" t="str">
-        <v>弘憲寺</v>
+        <v/>
       </c>
       <c r="O91" t="str">
-        <v>高松市錦町二丁目4-29</v>
+        <v>高松市円座町</v>
       </c>
       <c r="P91" t="str">
         <v/>
@@ -9167,7 +9731,7 @@
         <v/>
       </c>
       <c r="W91" t="str">
-        <v>1955-04-02</v>
+        <v>2004-03-05</v>
       </c>
       <c r="X91" t="str">
         <v/>
@@ -9226,7 +9790,7 @@
         <v>高松市</v>
       </c>
       <c r="H92" t="str">
-        <v>今岡古墳</v>
+        <v>庵治の船祭り</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -9238,16 +9802,16 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>県指定記念物</v>
+        <v>県指定民俗文化財</v>
       </c>
       <c r="M92" t="str">
-        <v>史跡</v>
+        <v>無形民俗</v>
       </c>
       <c r="N92" t="str">
         <v/>
       </c>
       <c r="O92" t="str">
-        <v>高松市鬼無町</v>
+        <v>高松市庵治町才田</v>
       </c>
       <c r="P92" t="str">
         <v/>
@@ -9271,7 +9835,7 @@
         <v/>
       </c>
       <c r="W92" t="str">
-        <v>1957-04-20</v>
+        <v>2009-06-26</v>
       </c>
       <c r="X92" t="str">
         <v/>
@@ -9330,7 +9894,7 @@
         <v>高松市</v>
       </c>
       <c r="H93" t="str">
-        <v>高松市茶臼山古墳</v>
+        <v>生駒親正夫妻墓所</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -9348,10 +9912,10 @@
         <v>史跡</v>
       </c>
       <c r="N93" t="str">
-        <v/>
+        <v>弘憲寺</v>
       </c>
       <c r="O93" t="str">
-        <v>高松市前田西町、新田町、東山崎町</v>
+        <v>高松市錦町二丁目4-29</v>
       </c>
       <c r="P93" t="str">
         <v/>
@@ -9375,7 +9939,7 @@
         <v/>
       </c>
       <c r="W93" t="str">
-        <v>1970-08-08</v>
+        <v>1955-04-02</v>
       </c>
       <c r="X93" t="str">
         <v/>
@@ -9434,7 +9998,7 @@
         <v>高松市</v>
       </c>
       <c r="H94" t="str">
-        <v>小比賀家築山庭園</v>
+        <v>今岡古墳</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -9449,13 +10013,13 @@
         <v>県指定記念物</v>
       </c>
       <c r="M94" t="str">
-        <v>名勝</v>
+        <v>史跡</v>
       </c>
       <c r="N94" t="str">
         <v/>
       </c>
       <c r="O94" t="str">
-        <v>高松市御厩町</v>
+        <v>高松市鬼無町</v>
       </c>
       <c r="P94" t="str">
         <v/>
@@ -9479,7 +10043,7 @@
         <v/>
       </c>
       <c r="W94" t="str">
-        <v>1971-04-30</v>
+        <v>1957-04-20</v>
       </c>
       <c r="X94" t="str">
         <v/>
@@ -9491,7 +10055,7 @@
         <v/>
       </c>
       <c r="AA94" t="str">
-        <v>【公開日】毎月第3日曜日。10：00～16：00。小比賀家宅内から見ることができる。</v>
+        <v/>
       </c>
       <c r="AB94" t="str">
         <v/>
@@ -9538,7 +10102,7 @@
         <v>高松市</v>
       </c>
       <c r="H95" t="str">
-        <v>船山神社のクス</v>
+        <v>高松市茶臼山古墳</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -9553,13 +10117,13 @@
         <v>県指定記念物</v>
       </c>
       <c r="M95" t="str">
-        <v>天然記念物</v>
+        <v>史跡</v>
       </c>
       <c r="N95" t="str">
-        <v>船山神社</v>
+        <v/>
       </c>
       <c r="O95" t="str">
-        <v>高松市仏生山町甲1149</v>
+        <v>高松市前田西町、新田町、東山崎町</v>
       </c>
       <c r="P95" t="str">
         <v/>
@@ -9583,7 +10147,7 @@
         <v/>
       </c>
       <c r="W95" t="str">
-        <v>1960-07-07</v>
+        <v>1970-08-08</v>
       </c>
       <c r="X95" t="str">
         <v/>
@@ -9642,7 +10206,7 @@
         <v>高松市</v>
       </c>
       <c r="H96" t="str">
-        <v>ソテツの岡</v>
+        <v>小比賀家築山庭園</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -9657,19 +10221,19 @@
         <v>県指定記念物</v>
       </c>
       <c r="M96" t="str">
-        <v>天然記念物</v>
+        <v>名勝</v>
       </c>
       <c r="N96" t="str">
-        <v>栗林公園</v>
+        <v/>
       </c>
       <c r="O96" t="str">
-        <v>高松市栗林町一丁目20-16</v>
+        <v>高松市御厩町</v>
       </c>
       <c r="P96" t="str">
         <v/>
       </c>
       <c r="Q96" t="str">
-        <v>087-833-7411</v>
+        <v/>
       </c>
       <c r="R96" t="str">
         <v/>
@@ -9687,10 +10251,10 @@
         <v/>
       </c>
       <c r="W96" t="str">
-        <v>1962-04-14</v>
+        <v>1971-04-30</v>
       </c>
       <c r="X96" t="str">
-        <v>月火水木金土日</v>
+        <v/>
       </c>
       <c r="Y96" t="str">
         <v/>
@@ -9699,7 +10263,7 @@
         <v/>
       </c>
       <c r="AA96" t="str">
-        <v>年中無休。【開園時間】ほぼ日の出から日没まで。季節によって異なる。HP参照のこと。</v>
+        <v>【公開日】毎月第3日曜日。10：00～16：00。小比賀家宅内から見ることができる。</v>
       </c>
       <c r="AB96" t="str">
         <v/>
@@ -9720,7 +10284,7 @@
         <v/>
       </c>
       <c r="AH96" t="str">
-        <v>https://www.my-kagawa.jp/ritsuringarden</v>
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -9746,7 +10310,7 @@
         <v>高松市</v>
       </c>
       <c r="H97" t="str">
-        <v>根上りカシ</v>
+        <v>船山神社のクス</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -9764,16 +10328,16 @@
         <v>天然記念物</v>
       </c>
       <c r="N97" t="str">
-        <v>栗林公園</v>
+        <v>船山神社</v>
       </c>
       <c r="O97" t="str">
-        <v>高松市栗林町一丁目20-16</v>
+        <v>高松市仏生山町甲1149</v>
       </c>
       <c r="P97" t="str">
         <v/>
       </c>
       <c r="Q97" t="str">
-        <v>087-833-7411</v>
+        <v/>
       </c>
       <c r="R97" t="str">
         <v/>
@@ -9791,10 +10355,10 @@
         <v/>
       </c>
       <c r="W97" t="str">
-        <v>1962-04-14</v>
+        <v>1960-07-07</v>
       </c>
       <c r="X97" t="str">
-        <v>月火水木金土日</v>
+        <v/>
       </c>
       <c r="Y97" t="str">
         <v/>
@@ -9803,7 +10367,7 @@
         <v/>
       </c>
       <c r="AA97" t="str">
-        <v>年中無休。【開園時間】ほぼ日の出から日没まで。季節によって異なる。HP参照のこと。</v>
+        <v/>
       </c>
       <c r="AB97" t="str">
         <v/>
@@ -9824,7 +10388,7 @@
         <v/>
       </c>
       <c r="AH97" t="str">
-        <v>https://www.my-kagawa.jp/ritsuringarden</v>
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -9850,7 +10414,7 @@
         <v>高松市</v>
       </c>
       <c r="H98" t="str">
-        <v>一瀬神社社叢</v>
+        <v>ソテツの岡</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -9868,16 +10432,16 @@
         <v>天然記念物</v>
       </c>
       <c r="N98" t="str">
-        <v>一瀬神社</v>
+        <v>栗林公園</v>
       </c>
       <c r="O98" t="str">
-        <v>高松市中山町1202-1</v>
+        <v>高松市栗林町一丁目20-16</v>
       </c>
       <c r="P98" t="str">
         <v/>
       </c>
       <c r="Q98" t="str">
-        <v/>
+        <v>087-833-7411</v>
       </c>
       <c r="R98" t="str">
         <v/>
@@ -9895,10 +10459,10 @@
         <v/>
       </c>
       <c r="W98" t="str">
-        <v>1971-04-30</v>
+        <v>1962-04-14</v>
       </c>
       <c r="X98" t="str">
-        <v/>
+        <v>月火水木金土日</v>
       </c>
       <c r="Y98" t="str">
         <v/>
@@ -9907,7 +10471,7 @@
         <v/>
       </c>
       <c r="AA98" t="str">
-        <v/>
+        <v>年中無休。【開園時間】ほぼ日の出から日没まで。季節によって異なる。HP参照のこと。</v>
       </c>
       <c r="AB98" t="str">
         <v/>
@@ -9928,7 +10492,7 @@
         <v/>
       </c>
       <c r="AH98" t="str">
-        <v/>
+        <v>https://www.my-kagawa.jp/ritsuringarden</v>
       </c>
     </row>
     <row r="99">
@@ -9954,7 +10518,7 @@
         <v>高松市</v>
       </c>
       <c r="H99" t="str">
-        <v>岩部八幡神社のイチョウ</v>
+        <v>根上りカシ</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -9972,16 +10536,16 @@
         <v>天然記念物</v>
       </c>
       <c r="N99" t="str">
-        <v>岩部八幡神社</v>
+        <v>栗林公園</v>
       </c>
       <c r="O99" t="str">
-        <v>高松市塩江町安原上692-1</v>
+        <v>高松市栗林町一丁目20-16</v>
       </c>
       <c r="P99" t="str">
         <v/>
       </c>
       <c r="Q99" t="str">
-        <v/>
+        <v>087-833-7411</v>
       </c>
       <c r="R99" t="str">
         <v/>
@@ -9999,10 +10563,10 @@
         <v/>
       </c>
       <c r="W99" t="str">
-        <v>1971-04-30</v>
+        <v>1962-04-14</v>
       </c>
       <c r="X99" t="str">
-        <v/>
+        <v>月火水木金土日</v>
       </c>
       <c r="Y99" t="str">
         <v/>
@@ -10011,7 +10575,7 @@
         <v/>
       </c>
       <c r="AA99" t="str">
-        <v/>
+        <v>年中無休。【開園時間】ほぼ日の出から日没まで。季節によって異なる。HP参照のこと。</v>
       </c>
       <c r="AB99" t="str">
         <v/>
@@ -10032,7 +10596,7 @@
         <v/>
       </c>
       <c r="AH99" t="str">
-        <v/>
+        <v>https://www.my-kagawa.jp/ritsuringarden</v>
       </c>
     </row>
     <row r="100">
@@ -10040,10 +10604,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>34.306284</v>
+        <v>0</v>
       </c>
       <c r="C100" t="str">
-        <v>133.963196</v>
+        <v>0</v>
       </c>
       <c r="D100" t="str">
         <v>37201</v>
@@ -10058,7 +10622,7 @@
         <v>高松市</v>
       </c>
       <c r="H100" t="str">
-        <v>国分寺北部小学校校門</v>
+        <v>一瀬神社社叢</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -10070,16 +10634,16 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>市指定有形文化財</v>
+        <v>県指定記念物</v>
       </c>
       <c r="M100" t="str">
-        <v>建造物</v>
+        <v>天然記念物</v>
       </c>
       <c r="N100" t="str">
-        <v>国分寺北部小学校</v>
+        <v>一瀬神社</v>
       </c>
       <c r="O100" t="str">
-        <v>高松市国分寺町新居1880</v>
+        <v>高松市中山町1202-1</v>
       </c>
       <c r="P100" t="str">
         <v/>
@@ -10103,7 +10667,7 @@
         <v/>
       </c>
       <c r="W100" t="str">
-        <v>1970-03-28</v>
+        <v>1971-04-30</v>
       </c>
       <c r="X100" t="str">
         <v/>
@@ -10162,7 +10726,7 @@
         <v>高松市</v>
       </c>
       <c r="H101" t="str">
-        <v>旧中石家住宅　主屋、隠居屋、納屋</v>
+        <v>岩部八幡神社のイチョウ</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -10174,22 +10738,22 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>市指定有形文化財</v>
+        <v>県指定記念物</v>
       </c>
       <c r="M101" t="str">
-        <v>建造物</v>
+        <v>天然記念物</v>
       </c>
       <c r="N101" t="str">
-        <v>公益財団法人　四国民家博物館（四国村）</v>
+        <v>岩部八幡神社</v>
       </c>
       <c r="O101" t="str">
-        <v>高松市屋島中町91</v>
+        <v>高松市塩江町安原上692-1</v>
       </c>
       <c r="P101" t="str">
         <v/>
       </c>
       <c r="Q101" t="str">
-        <v>087-843-3111</v>
+        <v/>
       </c>
       <c r="R101" t="str">
         <v/>
@@ -10207,19 +10771,19 @@
         <v/>
       </c>
       <c r="W101" t="str">
-        <v>1983-03-01</v>
+        <v>1971-04-30</v>
       </c>
       <c r="X101" t="str">
-        <v>月火水木金土日</v>
+        <v/>
       </c>
       <c r="Y101" t="str">
-        <v>08:30</v>
+        <v/>
       </c>
       <c r="Z101" t="str">
-        <v>17:30</v>
+        <v/>
       </c>
       <c r="AA101" t="str">
-        <v>年中無休。【閉園時間】18：00（4月～10月）、17：30（11月～3月）</v>
+        <v/>
       </c>
       <c r="AB101" t="str">
         <v/>
@@ -10240,7 +10804,7 @@
         <v/>
       </c>
       <c r="AH101" t="str">
-        <v>https://www.shikokumura.or.jp/</v>
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -10248,10 +10812,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="str">
-        <v>0</v>
+        <v>34.306284</v>
       </c>
       <c r="C102" t="str">
-        <v>0</v>
+        <v>133.963196</v>
       </c>
       <c r="D102" t="str">
         <v>37201</v>
@@ -10266,7 +10830,7 @@
         <v>高松市</v>
       </c>
       <c r="H102" t="str">
-        <v>小豆島の農村歌舞伎舞台</v>
+        <v>国分寺北部小学校校門</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -10284,16 +10848,16 @@
         <v>建造物</v>
       </c>
       <c r="N102" t="str">
-        <v>公益財団法人　四国民家博物館（四国村）</v>
+        <v>国分寺北部小学校</v>
       </c>
       <c r="O102" t="str">
-        <v>高松市屋島中町91</v>
+        <v>高松市国分寺町新居1880</v>
       </c>
       <c r="P102" t="str">
         <v/>
       </c>
       <c r="Q102" t="str">
-        <v>087-843-3111</v>
+        <v/>
       </c>
       <c r="R102" t="str">
         <v/>
@@ -10311,19 +10875,19 @@
         <v/>
       </c>
       <c r="W102" t="str">
-        <v>1983-03-01</v>
+        <v>1970-03-28</v>
       </c>
       <c r="X102" t="str">
-        <v>月火水木金土日</v>
+        <v/>
       </c>
       <c r="Y102" t="str">
-        <v>08:30</v>
+        <v/>
       </c>
       <c r="Z102" t="str">
-        <v>17:30</v>
+        <v/>
       </c>
       <c r="AA102" t="str">
-        <v>年中無休。【閉園時間】18：00（4月～10月）、17：30（11月～3月）</v>
+        <v/>
       </c>
       <c r="AB102" t="str">
         <v/>
@@ -10344,7 +10908,7 @@
         <v/>
       </c>
       <c r="AH102" t="str">
-        <v>https://www.shikokumura.or.jp/</v>
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -10370,7 +10934,7 @@
         <v>高松市</v>
       </c>
       <c r="H103" t="str">
-        <v>茶堂</v>
+        <v>旧中石家住宅　主屋、隠居屋、納屋</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -10415,7 +10979,7 @@
         <v/>
       </c>
       <c r="W103" t="str">
-        <v>1989-01-05</v>
+        <v>1983-03-01</v>
       </c>
       <c r="X103" t="str">
         <v>月火水木金土日</v>
@@ -10474,7 +11038,7 @@
         <v>高松市</v>
       </c>
       <c r="H104" t="str">
-        <v>旧吉野家住宅</v>
+        <v>小豆島の農村歌舞伎舞台</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -10519,7 +11083,7 @@
         <v/>
       </c>
       <c r="W104" t="str">
-        <v>1989-01-05</v>
+        <v>1983-03-01</v>
       </c>
       <c r="X104" t="str">
         <v>月火水木金土日</v>
@@ -10560,10 +11124,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>34.344341</v>
+        <v>0</v>
       </c>
       <c r="C105" t="str">
-        <v>134.05618</v>
+        <v>0</v>
       </c>
       <c r="D105" t="str">
         <v>37201</v>
@@ -10578,7 +11142,7 @@
         <v>高松市</v>
       </c>
       <c r="H105" t="str">
-        <v>旧新塩屋町小学校門柱</v>
+        <v>茶堂</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -10596,16 +11160,16 @@
         <v>建造物</v>
       </c>
       <c r="N105" t="str">
-        <v>高松市総合教育センター</v>
+        <v>公益財団法人　四国民家博物館（四国村）</v>
       </c>
       <c r="O105" t="str">
-        <v>高松市末広町5</v>
+        <v>高松市屋島中町91</v>
       </c>
       <c r="P105" t="str">
         <v/>
       </c>
       <c r="Q105" t="str">
-        <v/>
+        <v>087-843-3111</v>
       </c>
       <c r="R105" t="str">
         <v/>
@@ -10623,19 +11187,19 @@
         <v/>
       </c>
       <c r="W105" t="str">
-        <v>2011-03-08</v>
+        <v>1989-01-05</v>
       </c>
       <c r="X105" t="str">
-        <v/>
+        <v>月火水木金土日</v>
       </c>
       <c r="Y105" t="str">
-        <v/>
+        <v>08:30</v>
       </c>
       <c r="Z105" t="str">
-        <v/>
+        <v>17:30</v>
       </c>
       <c r="AA105" t="str">
-        <v/>
+        <v>年中無休。【閉園時間】18：00（4月～10月）、17：30（11月～3月）</v>
       </c>
       <c r="AB105" t="str">
         <v/>
@@ -10656,7 +11220,7 @@
         <v/>
       </c>
       <c r="AH105" t="str">
-        <v/>
+        <v>https://www.shikokumura.or.jp/</v>
       </c>
     </row>
     <row r="106">
@@ -10682,7 +11246,7 @@
         <v>高松市</v>
       </c>
       <c r="H106" t="str">
-        <v>生駒親正肖像画</v>
+        <v>旧吉野家住宅</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -10697,19 +11261,19 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M106" t="str">
-        <v>絵画</v>
+        <v>建造物</v>
       </c>
       <c r="N106" t="str">
-        <v>弘憲寺</v>
+        <v>公益財団法人　四国民家博物館（四国村）</v>
       </c>
       <c r="O106" t="str">
-        <v>高松市錦町二丁目4-29</v>
+        <v>高松市屋島中町91</v>
       </c>
       <c r="P106" t="str">
         <v/>
       </c>
       <c r="Q106" t="str">
-        <v/>
+        <v>087-843-3111</v>
       </c>
       <c r="R106" t="str">
         <v/>
@@ -10730,16 +11294,16 @@
         <v>1989-01-05</v>
       </c>
       <c r="X106" t="str">
-        <v/>
+        <v>月火水木金土日</v>
       </c>
       <c r="Y106" t="str">
-        <v/>
+        <v>08:30</v>
       </c>
       <c r="Z106" t="str">
-        <v/>
+        <v>17:30</v>
       </c>
       <c r="AA106" t="str">
-        <v/>
+        <v>年中無休。【閉園時間】18：00（4月～10月）、17：30（11月～3月）</v>
       </c>
       <c r="AB106" t="str">
         <v/>
@@ -10760,7 +11324,7 @@
         <v/>
       </c>
       <c r="AH106" t="str">
-        <v/>
+        <v>https://www.shikokumura.or.jp/</v>
       </c>
     </row>
     <row r="107">
@@ -10768,10 +11332,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>34.344189</v>
+        <v>34.344341</v>
       </c>
       <c r="C107" t="str">
-        <v>134.034412</v>
+        <v>134.05618</v>
       </c>
       <c r="D107" t="str">
         <v>37201</v>
@@ -10786,7 +11350,7 @@
         <v>高松市</v>
       </c>
       <c r="H107" t="str">
-        <v>紙本墨画淡彩玉蘭精舎祝宴図屏風   大原東野筆</v>
+        <v>旧新塩屋町小学校門柱</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -10801,19 +11365,19 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M107" t="str">
-        <v>絵画</v>
+        <v>建造物</v>
       </c>
       <c r="N107" t="str">
-        <v>高松市歴史資料館</v>
+        <v>高松市総合教育センター</v>
       </c>
       <c r="O107" t="str">
-        <v>高松市昭和町一丁目2-20</v>
+        <v>高松市末広町5</v>
       </c>
       <c r="P107" t="str">
         <v/>
       </c>
       <c r="Q107" t="str">
-        <v>087-861-4520</v>
+        <v/>
       </c>
       <c r="R107" t="str">
         <v/>
@@ -10831,19 +11395,19 @@
         <v/>
       </c>
       <c r="W107" t="str">
-        <v>2001-12-26</v>
+        <v>2011-03-08</v>
       </c>
       <c r="X107" t="str">
-        <v>火水木金土日</v>
+        <v/>
       </c>
       <c r="Y107" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="Z107" t="str">
-        <v>17:00</v>
+        <v/>
       </c>
       <c r="AA107" t="str">
-        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+        <v/>
       </c>
       <c r="AB107" t="str">
         <v/>
@@ -10864,7 +11428,7 @@
         <v/>
       </c>
       <c r="AH107" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
+        <v/>
       </c>
     </row>
     <row r="108">
@@ -10890,7 +11454,7 @@
         <v>高松市</v>
       </c>
       <c r="H108" t="str">
-        <v>金銅誕生釈迦仏立像</v>
+        <v>生駒親正肖像画</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -10905,13 +11469,13 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M108" t="str">
-        <v>彫刻</v>
+        <v>絵画</v>
       </c>
       <c r="N108" t="str">
-        <v>西方寺</v>
+        <v>弘憲寺</v>
       </c>
       <c r="O108" t="str">
-        <v>高松市西宝町三丁目9-27</v>
+        <v>高松市錦町二丁目4-29</v>
       </c>
       <c r="P108" t="str">
         <v/>
@@ -10976,10 +11540,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="str">
-        <v>0</v>
+        <v>34.344189</v>
       </c>
       <c r="C109" t="str">
-        <v>0</v>
+        <v>134.034412</v>
       </c>
       <c r="D109" t="str">
         <v>37201</v>
@@ -10994,7 +11558,7 @@
         <v>高松市</v>
       </c>
       <c r="H109" t="str">
-        <v>木造阿弥陀如来立像</v>
+        <v>紙本墨画淡彩玉蘭精舎祝宴図屏風   大原東野筆</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -11009,19 +11573,19 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M109" t="str">
-        <v>彫刻</v>
+        <v>絵画</v>
       </c>
       <c r="N109" t="str">
-        <v/>
+        <v>高松市歴史資料館</v>
       </c>
       <c r="O109" t="str">
-        <v>高松市室町</v>
+        <v>高松市昭和町一丁目2-20</v>
       </c>
       <c r="P109" t="str">
         <v/>
       </c>
       <c r="Q109" t="str">
-        <v/>
+        <v>087-861-4520</v>
       </c>
       <c r="R109" t="str">
         <v/>
@@ -11039,19 +11603,19 @@
         <v/>
       </c>
       <c r="W109" t="str">
-        <v>2010-03-10</v>
+        <v>2001-12-26</v>
       </c>
       <c r="X109" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y109" t="str">
-        <v/>
+        <v>09:00</v>
       </c>
       <c r="Z109" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA109" t="str">
-        <v/>
+        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
       </c>
       <c r="AB109" t="str">
         <v/>
@@ -11072,7 +11636,7 @@
         <v/>
       </c>
       <c r="AH109" t="str">
-        <v/>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
       </c>
     </row>
     <row r="110">
@@ -11098,7 +11662,7 @@
         <v>高松市</v>
       </c>
       <c r="H110" t="str">
-        <v>摩尼輪塔</v>
+        <v>金銅誕生釈迦仏立像</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -11113,13 +11677,13 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M110" t="str">
-        <v>工芸品</v>
+        <v>彫刻</v>
       </c>
       <c r="N110" t="str">
-        <v/>
+        <v>西方寺</v>
       </c>
       <c r="O110" t="str">
-        <v>高松市国分寺町新居</v>
+        <v>高松市西宝町三丁目9-27</v>
       </c>
       <c r="P110" t="str">
         <v/>
@@ -11143,7 +11707,7 @@
         <v/>
       </c>
       <c r="W110" t="str">
-        <v>1970-03-28</v>
+        <v>1989-01-05</v>
       </c>
       <c r="X110" t="str">
         <v/>
@@ -11184,10 +11748,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="str">
-        <v>34.34997</v>
+        <v>0</v>
       </c>
       <c r="C111" t="str">
-        <v>134.053336</v>
+        <v>0</v>
       </c>
       <c r="D111" t="str">
         <v>37201</v>
@@ -11202,7 +11766,7 @@
         <v>高松市</v>
       </c>
       <c r="H111" t="str">
-        <v>脇差  銘　讃州住盈永</v>
+        <v>木造阿弥陀如来立像</v>
       </c>
       <c r="I111" t="str">
         <v/>
@@ -11217,19 +11781,19 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M111" t="str">
-        <v>工芸品</v>
+        <v>彫刻</v>
       </c>
       <c r="N111" t="str">
-        <v>香川県立ミュージアム</v>
+        <v/>
       </c>
       <c r="O111" t="str">
-        <v>高松市玉藻町5-5</v>
+        <v>高松市室町</v>
       </c>
       <c r="P111" t="str">
         <v/>
       </c>
       <c r="Q111" t="str">
-        <v>087-822-0002</v>
+        <v/>
       </c>
       <c r="R111" t="str">
         <v/>
@@ -11247,19 +11811,19 @@
         <v/>
       </c>
       <c r="W111" t="str">
-        <v>1975-03-13</v>
+        <v>2010-03-10</v>
       </c>
       <c r="X111" t="str">
-        <v>火水木金土日</v>
+        <v/>
       </c>
       <c r="Y111" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="Z111" t="str">
-        <v>17:00</v>
+        <v/>
       </c>
       <c r="AA111" t="str">
-        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
+        <v/>
       </c>
       <c r="AB111" t="str">
         <v/>
@@ -11280,7 +11844,7 @@
         <v/>
       </c>
       <c r="AH111" t="str">
-        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -11288,10 +11852,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="str">
-        <v>34.34997</v>
+        <v>0</v>
       </c>
       <c r="C112" t="str">
-        <v>134.053336</v>
+        <v>0</v>
       </c>
       <c r="D112" t="str">
         <v>37201</v>
@@ -11306,7 +11870,7 @@
         <v>高松市</v>
       </c>
       <c r="H112" t="str">
-        <v>仏餉茶碗</v>
+        <v>摩尼輪塔</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -11324,16 +11888,16 @@
         <v>工芸品</v>
       </c>
       <c r="N112" t="str">
-        <v>香川県立ミュージアム</v>
+        <v/>
       </c>
       <c r="O112" t="str">
-        <v>高松市玉藻町5-5</v>
+        <v>高松市国分寺町新居</v>
       </c>
       <c r="P112" t="str">
         <v/>
       </c>
       <c r="Q112" t="str">
-        <v>087-822-0002</v>
+        <v/>
       </c>
       <c r="R112" t="str">
         <v/>
@@ -11351,19 +11915,19 @@
         <v/>
       </c>
       <c r="W112" t="str">
-        <v>1976-04-01</v>
+        <v>1970-03-28</v>
       </c>
       <c r="X112" t="str">
-        <v>火水木金土日</v>
+        <v/>
       </c>
       <c r="Y112" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="Z112" t="str">
-        <v>17:00</v>
+        <v/>
       </c>
       <c r="AA112" t="str">
-        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
+        <v/>
       </c>
       <c r="AB112" t="str">
         <v/>
@@ -11384,7 +11948,7 @@
         <v/>
       </c>
       <c r="AH112" t="str">
-        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -11392,10 +11956,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>0</v>
+        <v>34.34997</v>
       </c>
       <c r="C113" t="str">
-        <v>0</v>
+        <v>134.053336</v>
       </c>
       <c r="D113" t="str">
         <v>37201</v>
@@ -11410,7 +11974,7 @@
         <v>高松市</v>
       </c>
       <c r="H113" t="str">
-        <v>鰐口</v>
+        <v>脇差  銘　讃州住盈永</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -11428,16 +11992,16 @@
         <v>工芸品</v>
       </c>
       <c r="N113" t="str">
-        <v>椙尾神社</v>
+        <v>香川県立ミュージアム</v>
       </c>
       <c r="O113" t="str">
-        <v>高松市十川東町561</v>
+        <v>高松市玉藻町5-5</v>
       </c>
       <c r="P113" t="str">
         <v/>
       </c>
       <c r="Q113" t="str">
-        <v/>
+        <v>087-822-0002</v>
       </c>
       <c r="R113" t="str">
         <v/>
@@ -11455,19 +12019,19 @@
         <v/>
       </c>
       <c r="W113" t="str">
-        <v>1979-08-01</v>
+        <v>1975-03-13</v>
       </c>
       <c r="X113" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y113" t="str">
-        <v/>
+        <v>09:00</v>
       </c>
       <c r="Z113" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA113" t="str">
-        <v/>
+        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
       </c>
       <c r="AB113" t="str">
         <v/>
@@ -11488,7 +12052,7 @@
         <v/>
       </c>
       <c r="AH113" t="str">
-        <v/>
+        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
       </c>
     </row>
     <row r="114">
@@ -11496,10 +12060,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="str">
-        <v>0</v>
+        <v>34.34997</v>
       </c>
       <c r="C114" t="str">
-        <v>0</v>
+        <v>134.053336</v>
       </c>
       <c r="D114" t="str">
         <v>37201</v>
@@ -11514,7 +12078,7 @@
         <v>高松市</v>
       </c>
       <c r="H114" t="str">
-        <v>藤尾八幡神社奉納鏡</v>
+        <v>仏餉茶碗</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -11532,16 +12096,16 @@
         <v>工芸品</v>
       </c>
       <c r="N114" t="str">
-        <v>藤尾八幡神社</v>
+        <v>香川県立ミュージアム</v>
       </c>
       <c r="O114" t="str">
-        <v>高松市西植田町</v>
+        <v>高松市玉藻町5-5</v>
       </c>
       <c r="P114" t="str">
         <v/>
       </c>
       <c r="Q114" t="str">
-        <v/>
+        <v>087-822-0002</v>
       </c>
       <c r="R114" t="str">
         <v/>
@@ -11559,19 +12123,19 @@
         <v/>
       </c>
       <c r="W114" t="str">
-        <v>1999-08-05</v>
+        <v>1976-04-01</v>
       </c>
       <c r="X114" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y114" t="str">
-        <v/>
+        <v>09:00</v>
       </c>
       <c r="Z114" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA114" t="str">
-        <v/>
+        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
       </c>
       <c r="AB114" t="str">
         <v/>
@@ -11592,7 +12156,7 @@
         <v/>
       </c>
       <c r="AH114" t="str">
-        <v/>
+        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
       </c>
     </row>
     <row r="115">
@@ -11600,10 +12164,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>34.344189</v>
+        <v>0</v>
       </c>
       <c r="C115" t="str">
-        <v>134.034412</v>
+        <v>0</v>
       </c>
       <c r="D115" t="str">
         <v>37201</v>
@@ -11618,7 +12182,7 @@
         <v>高松市</v>
       </c>
       <c r="H115" t="str">
-        <v>本小札肩白紺糸おどし具足   二方白四十八間筋兜</v>
+        <v>鰐口</v>
       </c>
       <c r="I115" t="str">
         <v/>
@@ -11636,16 +12200,16 @@
         <v>工芸品</v>
       </c>
       <c r="N115" t="str">
-        <v>高松市歴史資料館</v>
+        <v>椙尾神社</v>
       </c>
       <c r="O115" t="str">
-        <v>高松市昭和町一丁目2-20</v>
+        <v>高松市十川東町561</v>
       </c>
       <c r="P115" t="str">
         <v/>
       </c>
       <c r="Q115" t="str">
-        <v>087-861-4520</v>
+        <v/>
       </c>
       <c r="R115" t="str">
         <v/>
@@ -11663,19 +12227,19 @@
         <v/>
       </c>
       <c r="W115" t="str">
-        <v>1999-08-05</v>
+        <v>1979-08-01</v>
       </c>
       <c r="X115" t="str">
-        <v>火水木金土日</v>
+        <v/>
       </c>
       <c r="Y115" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="Z115" t="str">
-        <v>17:00</v>
+        <v/>
       </c>
       <c r="AA115" t="str">
-        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+        <v/>
       </c>
       <c r="AB115" t="str">
         <v/>
@@ -11696,7 +12260,7 @@
         <v/>
       </c>
       <c r="AH115" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -11704,10 +12268,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>34.344189</v>
+        <v>0</v>
       </c>
       <c r="C116" t="str">
-        <v>134.034412</v>
+        <v>0</v>
       </c>
       <c r="D116" t="str">
         <v>37201</v>
@@ -11722,7 +12286,7 @@
         <v>高松市</v>
       </c>
       <c r="H116" t="str">
-        <v>剣  銘  則國</v>
+        <v>藤尾八幡神社奉納鏡</v>
       </c>
       <c r="I116" t="str">
         <v/>
@@ -11740,16 +12304,16 @@
         <v>工芸品</v>
       </c>
       <c r="N116" t="str">
-        <v>高松市歴史資料館</v>
+        <v>藤尾八幡神社</v>
       </c>
       <c r="O116" t="str">
-        <v>高松市昭和町一丁目2-20</v>
+        <v>高松市西植田町</v>
       </c>
       <c r="P116" t="str">
         <v/>
       </c>
       <c r="Q116" t="str">
-        <v>087-861-4520</v>
+        <v/>
       </c>
       <c r="R116" t="str">
         <v/>
@@ -11767,19 +12331,19 @@
         <v/>
       </c>
       <c r="W116" t="str">
-        <v>2007-04-10</v>
+        <v>1999-08-05</v>
       </c>
       <c r="X116" t="str">
-        <v>火水木金土日</v>
+        <v/>
       </c>
       <c r="Y116" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="Z116" t="str">
-        <v>17:00</v>
+        <v/>
       </c>
       <c r="AA116" t="str">
-        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+        <v/>
       </c>
       <c r="AB116" t="str">
         <v/>
@@ -11800,7 +12364,7 @@
         <v/>
       </c>
       <c r="AH116" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -11808,10 +12372,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>34.344347</v>
+        <v>34.344189</v>
       </c>
       <c r="C117" t="str">
-        <v>134.049095</v>
+        <v>134.034412</v>
       </c>
       <c r="D117" t="str">
         <v>37201</v>
@@ -11826,7 +12390,7 @@
         <v>高松市</v>
       </c>
       <c r="H117" t="str">
-        <v>狭貫彫堆黒松ヶ浦香合（忘貝香合）</v>
+        <v>本小札肩白紺糸おどし具足   二方白四十八間筋兜</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -11844,16 +12408,16 @@
         <v>工芸品</v>
       </c>
       <c r="N117" t="str">
-        <v>高松市美術館</v>
+        <v>高松市歴史資料館</v>
       </c>
       <c r="O117" t="str">
-        <v>高松市紺屋町10-4</v>
+        <v>高松市昭和町一丁目2-20</v>
       </c>
       <c r="P117" t="str">
         <v/>
       </c>
       <c r="Q117" t="str">
-        <v>087-823-1711</v>
+        <v>087-861-4520</v>
       </c>
       <c r="R117" t="str">
         <v/>
@@ -11871,19 +12435,19 @@
         <v/>
       </c>
       <c r="W117" t="str">
-        <v>2015-03-31</v>
+        <v>1999-08-05</v>
       </c>
       <c r="X117" t="str">
         <v>火水木金土日</v>
       </c>
       <c r="Y117" t="str">
-        <v>09:30</v>
+        <v>09:00</v>
       </c>
       <c r="Z117" t="str">
         <v>17:00</v>
       </c>
       <c r="AA117" t="str">
-        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/4）利用不可</v>
+        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
       </c>
       <c r="AB117" t="str">
         <v/>
@@ -11904,7 +12468,7 @@
         <v/>
       </c>
       <c r="AH117" t="str">
-        <v>https://www.city.takamatsu.kagawa.jp/museum/takamatsu/</v>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
       </c>
     </row>
     <row r="118">
@@ -11912,10 +12476,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>34.344347</v>
+        <v>34.344189</v>
       </c>
       <c r="C118" t="str">
-        <v>134.049095</v>
+        <v>134.034412</v>
       </c>
       <c r="D118" t="str">
         <v>37201</v>
@@ -11930,7 +12494,7 @@
         <v>高松市</v>
       </c>
       <c r="H118" t="str">
-        <v>堆朱篳篥筥</v>
+        <v>剣  銘  則國</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -11948,16 +12512,16 @@
         <v>工芸品</v>
       </c>
       <c r="N118" t="str">
-        <v>高松市美術館</v>
+        <v>高松市歴史資料館</v>
       </c>
       <c r="O118" t="str">
-        <v>高松市紺屋町10-4</v>
+        <v>高松市昭和町一丁目2-20</v>
       </c>
       <c r="P118" t="str">
         <v/>
       </c>
       <c r="Q118" t="str">
-        <v>087-823-1711</v>
+        <v>087-861-4520</v>
       </c>
       <c r="R118" t="str">
         <v/>
@@ -11975,19 +12539,19 @@
         <v/>
       </c>
       <c r="W118" t="str">
-        <v>2015-03-31</v>
+        <v>2007-04-10</v>
       </c>
       <c r="X118" t="str">
         <v>火水木金土日</v>
       </c>
       <c r="Y118" t="str">
-        <v>09:30</v>
+        <v>09:00</v>
       </c>
       <c r="Z118" t="str">
         <v>17:00</v>
       </c>
       <c r="AA118" t="str">
-        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/5）利用不可</v>
+        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
       </c>
       <c r="AB118" t="str">
         <v/>
@@ -12008,7 +12572,7 @@
         <v/>
       </c>
       <c r="AH118" t="str">
-        <v>https://www.city.takamatsu.kagawa.jp/museum/takamatsu/</v>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
       </c>
     </row>
     <row r="119">
@@ -12034,7 +12598,7 @@
         <v>高松市</v>
       </c>
       <c r="H119" t="str">
-        <v>讃岐彫堆朱手向山香盒</v>
+        <v>狭貫彫堆黒松ヶ浦香合（忘貝香合）</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -12091,7 +12655,7 @@
         <v>17:00</v>
       </c>
       <c r="AA119" t="str">
-        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/6）利用不可</v>
+        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/4）利用不可</v>
       </c>
       <c r="AB119" t="str">
         <v/>
@@ -12138,7 +12702,7 @@
         <v>高松市</v>
       </c>
       <c r="H120" t="str">
-        <v>彩色蒟醤水指棚</v>
+        <v>堆朱篳篥筥</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -12195,7 +12759,7 @@
         <v>17:00</v>
       </c>
       <c r="AA120" t="str">
-        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/7）利用不可</v>
+        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/5）利用不可</v>
       </c>
       <c r="AB120" t="str">
         <v/>
@@ -12224,10 +12788,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="str">
-        <v>34.344189</v>
+        <v>34.344347</v>
       </c>
       <c r="C121" t="str">
-        <v>134.034412</v>
+        <v>134.049095</v>
       </c>
       <c r="D121" t="str">
         <v>37201</v>
@@ -12242,7 +12806,7 @@
         <v>高松市</v>
       </c>
       <c r="H121" t="str">
-        <v>刀　銘　讃州住盈永　附　盈永文書</v>
+        <v>讃岐彫堆朱手向山香盒</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -12260,16 +12824,16 @@
         <v>工芸品</v>
       </c>
       <c r="N121" t="str">
-        <v>高松市歴史資料館</v>
+        <v>高松市美術館</v>
       </c>
       <c r="O121" t="str">
-        <v>高松市昭和町一丁目2-20</v>
+        <v>高松市紺屋町10-4</v>
       </c>
       <c r="P121" t="str">
         <v/>
       </c>
       <c r="Q121" t="str">
-        <v>087-861-4520</v>
+        <v>087-823-1711</v>
       </c>
       <c r="R121" t="str">
         <v/>
@@ -12287,19 +12851,19 @@
         <v/>
       </c>
       <c r="W121" t="str">
-        <v>2015-03-31、2016-03-31（文書を附指定）</v>
+        <v>2015-03-31</v>
       </c>
       <c r="X121" t="str">
         <v>火水木金土日</v>
       </c>
       <c r="Y121" t="str">
-        <v>09:00</v>
+        <v>09:30</v>
       </c>
       <c r="Z121" t="str">
         <v>17:00</v>
       </c>
       <c r="AA121" t="str">
-        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/6）利用不可</v>
       </c>
       <c r="AB121" t="str">
         <v/>
@@ -12320,7 +12884,7 @@
         <v/>
       </c>
       <c r="AH121" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
+        <v>https://www.city.takamatsu.kagawa.jp/museum/takamatsu/</v>
       </c>
     </row>
     <row r="122">
@@ -12328,10 +12892,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="str">
-        <v>34.34997</v>
+        <v>34.344347</v>
       </c>
       <c r="C122" t="str">
-        <v>134.053336</v>
+        <v>134.049095</v>
       </c>
       <c r="D122" t="str">
         <v>37201</v>
@@ -12346,7 +12910,7 @@
         <v>高松市</v>
       </c>
       <c r="H122" t="str">
-        <v>徳川家綱安堵判物案</v>
+        <v>彩色蒟醤水指棚</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -12361,19 +12925,19 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M122" t="str">
-        <v>書跡</v>
+        <v>工芸品</v>
       </c>
       <c r="N122" t="str">
-        <v>香川県立ミュージアム</v>
+        <v>高松市美術館</v>
       </c>
       <c r="O122" t="str">
-        <v>高松市玉藻町5-5</v>
+        <v>高松市紺屋町10-4</v>
       </c>
       <c r="P122" t="str">
         <v/>
       </c>
       <c r="Q122" t="str">
-        <v>087-822-0002</v>
+        <v>087-823-1711</v>
       </c>
       <c r="R122" t="str">
         <v/>
@@ -12391,19 +12955,19 @@
         <v/>
       </c>
       <c r="W122" t="str">
-        <v>1975-03-13</v>
+        <v>2015-03-31</v>
       </c>
       <c r="X122" t="str">
         <v>火水木金土日</v>
       </c>
       <c r="Y122" t="str">
-        <v>09:00</v>
+        <v>09:30</v>
       </c>
       <c r="Z122" t="str">
         <v>17:00</v>
       </c>
       <c r="AA122" t="str">
-        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
+        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/7）利用不可</v>
       </c>
       <c r="AB122" t="str">
         <v/>
@@ -12424,7 +12988,7 @@
         <v/>
       </c>
       <c r="AH122" t="str">
-        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
+        <v>https://www.city.takamatsu.kagawa.jp/museum/takamatsu/</v>
       </c>
     </row>
     <row r="123">
@@ -12432,10 +12996,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>34.34997</v>
+        <v>34.344189</v>
       </c>
       <c r="C123" t="str">
-        <v>134.053336</v>
+        <v>134.034412</v>
       </c>
       <c r="D123" t="str">
         <v>37201</v>
@@ -12450,7 +13014,7 @@
         <v>高松市</v>
       </c>
       <c r="H123" t="str">
-        <v>永井尚庸・小笠原長賴連署奉書</v>
+        <v>刀　銘　讃州住盈永　附　盈永文書</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -12465,19 +13029,19 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M123" t="str">
-        <v>書跡</v>
+        <v>工芸品</v>
       </c>
       <c r="N123" t="str">
-        <v>香川県立ミュージアム</v>
+        <v>高松市歴史資料館</v>
       </c>
       <c r="O123" t="str">
-        <v>高松市玉藻町5-5</v>
+        <v>高松市昭和町一丁目2-20</v>
       </c>
       <c r="P123" t="str">
         <v/>
       </c>
       <c r="Q123" t="str">
-        <v>087-822-0002</v>
+        <v>087-861-4520</v>
       </c>
       <c r="R123" t="str">
         <v/>
@@ -12495,7 +13059,7 @@
         <v/>
       </c>
       <c r="W123" t="str">
-        <v>1975-03-13</v>
+        <v>2015-03-31、2016-03-31（文書を附指定）</v>
       </c>
       <c r="X123" t="str">
         <v>火水木金土日</v>
@@ -12507,7 +13071,7 @@
         <v>17:00</v>
       </c>
       <c r="AA123" t="str">
-        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
+        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
       </c>
       <c r="AB123" t="str">
         <v/>
@@ -12528,7 +13092,7 @@
         <v/>
       </c>
       <c r="AH123" t="str">
-        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
       </c>
     </row>
     <row r="124">
@@ -12554,7 +13118,7 @@
         <v>高松市</v>
       </c>
       <c r="H124" t="str">
-        <v>松平賴重筆   和歌幅</v>
+        <v>徳川家綱安堵判物案</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -12658,7 +13222,7 @@
         <v>高松市</v>
       </c>
       <c r="H125" t="str">
-        <v>松平賴重  短冊屏風</v>
+        <v>永井尚庸・小笠原長賴連署奉書</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -12703,7 +13267,7 @@
         <v/>
       </c>
       <c r="W125" t="str">
-        <v>1977-08-01</v>
+        <v>1975-03-13</v>
       </c>
       <c r="X125" t="str">
         <v>火水木金土日</v>
@@ -12744,10 +13308,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>34.344189</v>
+        <v>34.34997</v>
       </c>
       <c r="C126" t="str">
-        <v>134.034412</v>
+        <v>134.053336</v>
       </c>
       <c r="D126" t="str">
         <v>37201</v>
@@ -12762,7 +13326,7 @@
         <v>高松市</v>
       </c>
       <c r="H126" t="str">
-        <v>生駒家時代讃岐高松城屋敷割図  付同引伸図</v>
+        <v>松平賴重筆   和歌幅</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -12780,16 +13344,16 @@
         <v>書跡</v>
       </c>
       <c r="N126" t="str">
-        <v>高松市歴史資料館</v>
+        <v>香川県立ミュージアム</v>
       </c>
       <c r="O126" t="str">
-        <v>高松市昭和町一丁目2-20</v>
+        <v>高松市玉藻町5-5</v>
       </c>
       <c r="P126" t="str">
         <v/>
       </c>
       <c r="Q126" t="str">
-        <v>087-861-4520</v>
+        <v>087-822-0002</v>
       </c>
       <c r="R126" t="str">
         <v/>
@@ -12819,7 +13383,7 @@
         <v>17:00</v>
       </c>
       <c r="AA126" t="str">
-        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
       </c>
       <c r="AB126" t="str">
         <v/>
@@ -12840,7 +13404,7 @@
         <v/>
       </c>
       <c r="AH126" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
+        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
       </c>
     </row>
     <row r="127">
@@ -12848,10 +13412,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="str">
-        <v>34.344189</v>
+        <v>34.34997</v>
       </c>
       <c r="C127" t="str">
-        <v>134.034412</v>
+        <v>134.053336</v>
       </c>
       <c r="D127" t="str">
         <v>37201</v>
@@ -12866,7 +13430,7 @@
         <v>高松市</v>
       </c>
       <c r="H127" t="str">
-        <v>讃岐国一宮田村大社壁書</v>
+        <v>松平賴重  短冊屏風</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -12884,16 +13448,16 @@
         <v>書跡</v>
       </c>
       <c r="N127" t="str">
-        <v>高松市歴史資料館</v>
+        <v>香川県立ミュージアム</v>
       </c>
       <c r="O127" t="str">
-        <v>高松市昭和町一丁目2-20</v>
+        <v>高松市玉藻町5-5</v>
       </c>
       <c r="P127" t="str">
         <v/>
       </c>
       <c r="Q127" t="str">
-        <v>087-861-4520</v>
+        <v>087-822-0002</v>
       </c>
       <c r="R127" t="str">
         <v/>
@@ -12923,7 +13487,7 @@
         <v>17:00</v>
       </c>
       <c r="AA127" t="str">
-        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+        <v>入館は16：30まで。【休館日】月曜日（祝休日の場合は、翌火曜日）。年末年始など。</v>
       </c>
       <c r="AB127" t="str">
         <v/>
@@ -12944,7 +13508,7 @@
         <v/>
       </c>
       <c r="AH127" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
+        <v>https://www.pref.kagawa.lg.jp/kmuseum/</v>
       </c>
     </row>
     <row r="128">
@@ -12952,10 +13516,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>0</v>
+        <v>34.344189</v>
       </c>
       <c r="C128" t="str">
-        <v>0</v>
+        <v>134.034412</v>
       </c>
       <c r="D128" t="str">
         <v>37201</v>
@@ -12970,7 +13534,7 @@
         <v>高松市</v>
       </c>
       <c r="H128" t="str">
-        <v>大般若波羅蜜多経</v>
+        <v>生駒家時代讃岐高松城屋敷割図  付同引伸図</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -12988,16 +13552,16 @@
         <v>書跡</v>
       </c>
       <c r="N128" t="str">
-        <v>願成寺</v>
+        <v>高松市歴史資料館</v>
       </c>
       <c r="O128" t="str">
-        <v>高松市庵治町井谷1625</v>
+        <v>高松市昭和町一丁目2-20</v>
       </c>
       <c r="P128" t="str">
         <v/>
       </c>
       <c r="Q128" t="str">
-        <v/>
+        <v>087-861-4520</v>
       </c>
       <c r="R128" t="str">
         <v/>
@@ -13015,19 +13579,19 @@
         <v/>
       </c>
       <c r="W128" t="str">
-        <v>1982-01-13</v>
+        <v>1975-03-13</v>
       </c>
       <c r="X128" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y128" t="str">
-        <v/>
+        <v>09:00</v>
       </c>
       <c r="Z128" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA128" t="str">
-        <v/>
+        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
       </c>
       <c r="AB128" t="str">
         <v/>
@@ -13048,7 +13612,7 @@
         <v/>
       </c>
       <c r="AH128" t="str">
-        <v/>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
       </c>
     </row>
     <row r="129">
@@ -13056,10 +13620,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>34.239572</v>
+        <v>34.344189</v>
       </c>
       <c r="C129" t="str">
-        <v>134.021774</v>
+        <v>134.034412</v>
       </c>
       <c r="D129" t="str">
         <v>37201</v>
@@ -13074,7 +13638,7 @@
         <v>高松市</v>
       </c>
       <c r="H129" t="str">
-        <v>由佐家文書</v>
+        <v>讃岐国一宮田村大社壁書</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -13089,19 +13653,19 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M129" t="str">
-        <v>古文書</v>
+        <v>書跡</v>
       </c>
       <c r="N129" t="str">
-        <v>香南歴史民俗郷土館</v>
+        <v>高松市歴史資料館</v>
       </c>
       <c r="O129" t="str">
-        <v>高松市香南町由佐253-1</v>
+        <v>高松市昭和町一丁目2-20</v>
       </c>
       <c r="P129" t="str">
         <v/>
       </c>
       <c r="Q129" t="str">
-        <v>087-879-0717</v>
+        <v>087-861-4520</v>
       </c>
       <c r="R129" t="str">
         <v/>
@@ -13119,7 +13683,7 @@
         <v/>
       </c>
       <c r="W129" t="str">
-        <v>2009-01-09</v>
+        <v>1977-08-01</v>
       </c>
       <c r="X129" t="str">
         <v>火水木金土日</v>
@@ -13131,7 +13695,7 @@
         <v>17:00</v>
       </c>
       <c r="AA129" t="str">
-        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
       </c>
       <c r="AB129" t="str">
         <v/>
@@ -13152,7 +13716,7 @@
         <v/>
       </c>
       <c r="AH129" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/konan.html</v>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
       </c>
     </row>
     <row r="130">
@@ -13178,7 +13742,7 @@
         <v>高松市</v>
       </c>
       <c r="H130" t="str">
-        <v>楠尾神社経塚出土遺物</v>
+        <v>大般若波羅蜜多経</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -13193,13 +13757,13 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M130" t="str">
-        <v>考古資料</v>
+        <v>書跡</v>
       </c>
       <c r="N130" t="str">
-        <v>楠尾神社</v>
+        <v>願成寺</v>
       </c>
       <c r="O130" t="str">
-        <v>高松市国分寺町新居3369</v>
+        <v>高松市庵治町井谷1625</v>
       </c>
       <c r="P130" t="str">
         <v/>
@@ -13223,7 +13787,7 @@
         <v/>
       </c>
       <c r="W130" t="str">
-        <v>1970-03-28</v>
+        <v>1982-01-13</v>
       </c>
       <c r="X130" t="str">
         <v/>
@@ -13264,10 +13828,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>0</v>
+        <v>34.239572</v>
       </c>
       <c r="C131" t="str">
-        <v>0</v>
+        <v>134.021774</v>
       </c>
       <c r="D131" t="str">
         <v>37201</v>
@@ -13282,7 +13846,7 @@
         <v>高松市</v>
       </c>
       <c r="H131" t="str">
-        <v>石船石棺</v>
+        <v>由佐家文書</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -13297,19 +13861,19 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M131" t="str">
-        <v>考古資料</v>
+        <v>古文書</v>
       </c>
       <c r="N131" t="str">
-        <v>石船天満宮</v>
+        <v>香南歴史民俗郷土館</v>
       </c>
       <c r="O131" t="str">
-        <v>高松市国分寺町新名1879</v>
+        <v>高松市香南町由佐253-1</v>
       </c>
       <c r="P131" t="str">
         <v/>
       </c>
       <c r="Q131" t="str">
-        <v/>
+        <v>087-879-0717</v>
       </c>
       <c r="R131" t="str">
         <v/>
@@ -13327,19 +13891,19 @@
         <v/>
       </c>
       <c r="W131" t="str">
-        <v>1970-03-28</v>
+        <v>2009-01-09</v>
       </c>
       <c r="X131" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y131" t="str">
-        <v/>
+        <v>09:00</v>
       </c>
       <c r="Z131" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA131" t="str">
-        <v/>
+        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
       </c>
       <c r="AB131" t="str">
         <v/>
@@ -13360,7 +13924,7 @@
         <v/>
       </c>
       <c r="AH131" t="str">
-        <v/>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/konan.html</v>
       </c>
     </row>
     <row r="132">
@@ -13386,7 +13950,7 @@
         <v>高松市</v>
       </c>
       <c r="H132" t="str">
-        <v>御城俊禅蒐集古瓦</v>
+        <v>楠尾神社経塚出土遺物</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -13404,10 +13968,10 @@
         <v>考古資料</v>
       </c>
       <c r="N132" t="str">
-        <v>洲崎寺</v>
+        <v>楠尾神社</v>
       </c>
       <c r="O132" t="str">
-        <v>高松市牟礼町牟礼269１</v>
+        <v>高松市国分寺町新居3369</v>
       </c>
       <c r="P132" t="str">
         <v/>
@@ -13431,7 +13995,7 @@
         <v/>
       </c>
       <c r="W132" t="str">
-        <v>1976-04-01</v>
+        <v>1970-03-28</v>
       </c>
       <c r="X132" t="str">
         <v/>
@@ -13480,6 +14044,9 @@
       <c r="D133" t="str">
         <v>37201</v>
       </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
       <c r="F133" t="str">
         <v>香川県</v>
       </c>
@@ -13487,7 +14054,16 @@
         <v>高松市</v>
       </c>
       <c r="H133" t="str">
-        <v>相作馬塚古墳竪穴式石室出土品</v>
+        <v>石船石棺</v>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v/>
       </c>
       <c r="L133" t="str">
         <v>市指定有形文化財</v>
@@ -13496,16 +14072,67 @@
         <v>考古資料</v>
       </c>
       <c r="N133" t="str">
-        <v>高松市埋蔵文化財センター</v>
+        <v>石船天満宮</v>
       </c>
       <c r="O133" t="str">
-        <v>高松市番町一丁目5-1</v>
+        <v>高松市国分寺町新名1879</v>
+      </c>
+      <c r="P133" t="str">
+        <v/>
       </c>
       <c r="Q133" t="str">
-        <v>087-823-2714</v>
+        <v/>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
+        <v/>
+      </c>
+      <c r="T133" t="str">
+        <v/>
+      </c>
+      <c r="U133" t="str">
+        <v/>
+      </c>
+      <c r="V133" t="str">
+        <v/>
       </c>
       <c r="W133" t="str">
-        <v>2025-03-28</v>
+        <v>1970-03-28</v>
+      </c>
+      <c r="X133" t="str">
+        <v/>
+      </c>
+      <c r="Y133" t="str">
+        <v/>
+      </c>
+      <c r="Z133" t="str">
+        <v/>
+      </c>
+      <c r="AA133" t="str">
+        <v/>
+      </c>
+      <c r="AB133" t="str">
+        <v/>
+      </c>
+      <c r="AC133" t="str">
+        <v/>
+      </c>
+      <c r="AD133" t="str">
+        <v/>
+      </c>
+      <c r="AE133" t="str">
+        <v/>
+      </c>
+      <c r="AF133" t="str">
+        <v/>
+      </c>
+      <c r="AG133" t="str">
+        <v/>
+      </c>
+      <c r="AH133" t="str">
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -13521,6 +14148,9 @@
       <c r="D134" t="str">
         <v>37201</v>
       </c>
+      <c r="E134" t="str">
+        <v/>
+      </c>
       <c r="F134" t="str">
         <v>香川県</v>
       </c>
@@ -13528,7 +14158,16 @@
         <v>高松市</v>
       </c>
       <c r="H134" t="str">
-        <v>天満・宮西遺跡出土銅鐸</v>
+        <v>御城俊禅蒐集古瓦</v>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v/>
       </c>
       <c r="L134" t="str">
         <v>市指定有形文化財</v>
@@ -13537,16 +14176,67 @@
         <v>考古資料</v>
       </c>
       <c r="N134" t="str">
-        <v>高松市埋蔵文化財センター</v>
+        <v>洲崎寺</v>
       </c>
       <c r="O134" t="str">
-        <v>高松市番町一丁目5-1</v>
+        <v>高松市牟礼町牟礼269１</v>
+      </c>
+      <c r="P134" t="str">
+        <v/>
       </c>
       <c r="Q134" t="str">
-        <v>087-823-2714</v>
+        <v/>
+      </c>
+      <c r="R134" t="str">
+        <v/>
+      </c>
+      <c r="S134" t="str">
+        <v/>
+      </c>
+      <c r="T134" t="str">
+        <v/>
+      </c>
+      <c r="U134" t="str">
+        <v/>
+      </c>
+      <c r="V134" t="str">
+        <v/>
       </c>
       <c r="W134" t="str">
-        <v>2019-03-15</v>
+        <v>1976-04-01</v>
+      </c>
+      <c r="X134" t="str">
+        <v/>
+      </c>
+      <c r="Y134" t="str">
+        <v/>
+      </c>
+      <c r="Z134" t="str">
+        <v/>
+      </c>
+      <c r="AA134" t="str">
+        <v/>
+      </c>
+      <c r="AB134" t="str">
+        <v/>
+      </c>
+      <c r="AC134" t="str">
+        <v/>
+      </c>
+      <c r="AD134" t="str">
+        <v/>
+      </c>
+      <c r="AE134" t="str">
+        <v/>
+      </c>
+      <c r="AF134" t="str">
+        <v/>
+      </c>
+      <c r="AG134" t="str">
+        <v/>
+      </c>
+      <c r="AH134" t="str">
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -13562,6 +14252,9 @@
       <c r="D135" t="str">
         <v>37201</v>
       </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
       <c r="F135" t="str">
         <v>香川県</v>
       </c>
@@ -13569,7 +14262,16 @@
         <v>高松市</v>
       </c>
       <c r="H135" t="str">
-        <v>伝香川町浅野出土石棺</v>
+        <v>相作馬塚古墳竪穴式石室出土品</v>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v/>
       </c>
       <c r="L135" t="str">
         <v>市指定有形文化財</v>
@@ -13578,13 +14280,67 @@
         <v>考古資料</v>
       </c>
       <c r="N135" t="str">
-        <v>浅野小学校</v>
+        <v>高松市埋蔵文化財センター</v>
       </c>
       <c r="O135" t="str">
-        <v>高松市香川町浅野</v>
+        <v>高松市番町一丁目5-1</v>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" t="str">
+        <v>087-823-2714</v>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+      <c r="S135" t="str">
+        <v/>
+      </c>
+      <c r="T135" t="str">
+        <v/>
+      </c>
+      <c r="U135" t="str">
+        <v/>
+      </c>
+      <c r="V135" t="str">
+        <v/>
       </c>
       <c r="W135" t="str">
-        <v>2023-04-14</v>
+        <v>2025-03-28</v>
+      </c>
+      <c r="X135" t="str">
+        <v/>
+      </c>
+      <c r="Y135" t="str">
+        <v/>
+      </c>
+      <c r="Z135" t="str">
+        <v/>
+      </c>
+      <c r="AA135" t="str">
+        <v/>
+      </c>
+      <c r="AB135" t="str">
+        <v/>
+      </c>
+      <c r="AC135" t="str">
+        <v/>
+      </c>
+      <c r="AD135" t="str">
+        <v/>
+      </c>
+      <c r="AE135" t="str">
+        <v/>
+      </c>
+      <c r="AF135" t="str">
+        <v/>
+      </c>
+      <c r="AG135" t="str">
+        <v/>
+      </c>
+      <c r="AH135" t="str">
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -13592,10 +14348,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="str">
-        <v>34.344189</v>
+        <v>0</v>
       </c>
       <c r="C136" t="str">
-        <v>134.034412</v>
+        <v>0</v>
       </c>
       <c r="D136" t="str">
         <v>37201</v>
@@ -13610,7 +14366,7 @@
         <v>高松市</v>
       </c>
       <c r="H136" t="str">
-        <v>大空遺跡出土弥生土器  ５３点</v>
+        <v>天満・宮西遺跡出土銅鐸</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -13628,16 +14384,16 @@
         <v>考古資料</v>
       </c>
       <c r="N136" t="str">
-        <v>高松市歴史資料館</v>
+        <v>高松市埋蔵文化財センター</v>
       </c>
       <c r="O136" t="str">
-        <v>高松市昭和町一丁目2-20</v>
+        <v>高松市番町一丁目5-1</v>
       </c>
       <c r="P136" t="str">
         <v/>
       </c>
       <c r="Q136" t="str">
-        <v>087-861-4520</v>
+        <v>087-823-2714</v>
       </c>
       <c r="R136" t="str">
         <v/>
@@ -13655,19 +14411,19 @@
         <v/>
       </c>
       <c r="W136" t="str">
-        <v>1998-06-01</v>
+        <v>2019-03-15</v>
       </c>
       <c r="X136" t="str">
-        <v>火水木金土日</v>
+        <v/>
       </c>
       <c r="Y136" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="Z136" t="str">
-        <v>17:00</v>
+        <v/>
       </c>
       <c r="AA136" t="str">
-        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+        <v/>
       </c>
       <c r="AB136" t="str">
         <v/>
@@ -13688,7 +14444,7 @@
         <v/>
       </c>
       <c r="AH136" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -13696,14 +14452,17 @@
         <v>136</v>
       </c>
       <c r="B137" t="str">
-        <v>34.344189</v>
+        <v>0</v>
       </c>
       <c r="C137" t="str">
-        <v>134.034412</v>
+        <v>0</v>
       </c>
       <c r="D137" t="str">
         <v>37201</v>
       </c>
+      <c r="E137" t="str">
+        <v/>
+      </c>
       <c r="F137" t="str">
         <v>香川県</v>
       </c>
@@ -13711,7 +14470,16 @@
         <v>高松市</v>
       </c>
       <c r="H137" t="str">
-        <v>鶴尾神社４号墳出土獣帯方格規矩四神鏡</v>
+        <v>伝香川町浅野出土石棺</v>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v/>
       </c>
       <c r="L137" t="str">
         <v>市指定有形文化財</v>
@@ -13720,31 +14488,67 @@
         <v>考古資料</v>
       </c>
       <c r="N137" t="str">
-        <v>高松市歴史資料館</v>
+        <v>浅野小学校</v>
       </c>
       <c r="O137" t="str">
-        <v>高松市昭和町一丁目2-20</v>
+        <v>高松市香川町浅野</v>
+      </c>
+      <c r="P137" t="str">
+        <v/>
       </c>
       <c r="Q137" t="str">
-        <v>087-861-4520</v>
+        <v/>
+      </c>
+      <c r="R137" t="str">
+        <v/>
+      </c>
+      <c r="S137" t="str">
+        <v/>
+      </c>
+      <c r="T137" t="str">
+        <v/>
+      </c>
+      <c r="U137" t="str">
+        <v/>
+      </c>
+      <c r="V137" t="str">
+        <v/>
       </c>
       <c r="W137" t="str">
-        <v>2021-03-31</v>
+        <v>2023-04-14</v>
       </c>
       <c r="X137" t="str">
-        <v>火水木金土日</v>
+        <v/>
       </c>
       <c r="Y137" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="Z137" t="str">
-        <v>17:00</v>
+        <v/>
       </c>
       <c r="AA137" t="str">
-        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+        <v/>
+      </c>
+      <c r="AB137" t="str">
+        <v/>
+      </c>
+      <c r="AC137" t="str">
+        <v/>
+      </c>
+      <c r="AD137" t="str">
+        <v/>
+      </c>
+      <c r="AE137" t="str">
+        <v/>
+      </c>
+      <c r="AF137" t="str">
+        <v/>
+      </c>
+      <c r="AG137" t="str">
+        <v/>
       </c>
       <c r="AH137" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
+        <v/>
       </c>
     </row>
     <row r="138">
@@ -13770,7 +14574,7 @@
         <v>高松市</v>
       </c>
       <c r="H138" t="str">
-        <v>山内村史</v>
+        <v>大空遺跡出土弥生土器  ５３点</v>
       </c>
       <c r="I138" t="str">
         <v/>
@@ -13785,7 +14589,7 @@
         <v>市指定有形文化財</v>
       </c>
       <c r="M138" t="str">
-        <v>歴史資料</v>
+        <v>考古資料</v>
       </c>
       <c r="N138" t="str">
         <v>高松市歴史資料館</v>
@@ -13815,7 +14619,7 @@
         <v/>
       </c>
       <c r="W138" t="str">
-        <v>1970-10-15</v>
+        <v>1998-06-01</v>
       </c>
       <c r="X138" t="str">
         <v>火水木金土日</v>
@@ -13864,6 +14668,9 @@
       <c r="D139" t="str">
         <v>37201</v>
       </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
       <c r="F139" t="str">
         <v>香川県</v>
       </c>
@@ -13871,13 +14678,22 @@
         <v>高松市</v>
       </c>
       <c r="H139" t="str">
-        <v>讃岐国絵図</v>
+        <v>鶴尾神社４号墳出土獣帯方格規矩四神鏡</v>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v/>
       </c>
       <c r="L139" t="str">
         <v>市指定有形文化財</v>
       </c>
       <c r="M139" t="str">
-        <v>歴史資料</v>
+        <v>考古資料</v>
       </c>
       <c r="N139" t="str">
         <v>高松市歴史資料館</v>
@@ -13885,11 +14701,29 @@
       <c r="O139" t="str">
         <v>高松市昭和町一丁目2-20</v>
       </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
       <c r="Q139" t="str">
         <v>087-861-4520</v>
       </c>
+      <c r="R139" t="str">
+        <v/>
+      </c>
+      <c r="S139" t="str">
+        <v/>
+      </c>
+      <c r="T139" t="str">
+        <v/>
+      </c>
+      <c r="U139" t="str">
+        <v/>
+      </c>
+      <c r="V139" t="str">
+        <v/>
+      </c>
       <c r="W139" t="str">
-        <v>2017-03-31</v>
+        <v>2021-03-31</v>
       </c>
       <c r="X139" t="str">
         <v>火水木金土日</v>
@@ -13902,6 +14736,27 @@
       </c>
       <c r="AA139" t="str">
         <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+      </c>
+      <c r="AB139" t="str">
+        <v/>
+      </c>
+      <c r="AC139" t="str">
+        <v/>
+      </c>
+      <c r="AD139" t="str">
+        <v/>
+      </c>
+      <c r="AE139" t="str">
+        <v/>
+      </c>
+      <c r="AF139" t="str">
+        <v/>
+      </c>
+      <c r="AG139" t="str">
+        <v/>
+      </c>
+      <c r="AH139" t="str">
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
       </c>
     </row>
     <row r="140">
@@ -13917,6 +14772,9 @@
       <c r="D140" t="str">
         <v>37201</v>
       </c>
+      <c r="E140" t="str">
+        <v/>
+      </c>
       <c r="F140" t="str">
         <v>香川県</v>
       </c>
@@ -13924,7 +14782,16 @@
         <v>高松市</v>
       </c>
       <c r="H140" t="str">
-        <v>高松城天守鯱</v>
+        <v>山内村史</v>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
+        <v/>
       </c>
       <c r="L140" t="str">
         <v>市指定有形文化財</v>
@@ -13938,11 +14805,29 @@
       <c r="O140" t="str">
         <v>高松市昭和町一丁目2-20</v>
       </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
       <c r="Q140" t="str">
         <v>087-861-4520</v>
       </c>
+      <c r="R140" t="str">
+        <v/>
+      </c>
+      <c r="S140" t="str">
+        <v/>
+      </c>
+      <c r="T140" t="str">
+        <v/>
+      </c>
+      <c r="U140" t="str">
+        <v/>
+      </c>
+      <c r="V140" t="str">
+        <v/>
+      </c>
       <c r="W140" t="str">
-        <v>2018-03-30</v>
+        <v>1970-10-15</v>
       </c>
       <c r="X140" t="str">
         <v>火水木金土日</v>
@@ -13955,6 +14840,27 @@
       </c>
       <c r="AA140" t="str">
         <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
+      </c>
+      <c r="AB140" t="str">
+        <v/>
+      </c>
+      <c r="AC140" t="str">
+        <v/>
+      </c>
+      <c r="AD140" t="str">
+        <v/>
+      </c>
+      <c r="AE140" t="str">
+        <v/>
+      </c>
+      <c r="AF140" t="str">
+        <v/>
+      </c>
+      <c r="AG140" t="str">
+        <v/>
+      </c>
+      <c r="AH140" t="str">
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/rekishi/index.html</v>
       </c>
     </row>
     <row r="141">
@@ -13962,10 +14868,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="str">
-        <v>34.344347</v>
+        <v>34.344189</v>
       </c>
       <c r="C141" t="str">
-        <v>134.049095</v>
+        <v>134.034412</v>
       </c>
       <c r="D141" t="str">
         <v>37201</v>
@@ -13980,7 +14886,7 @@
         <v>高松市</v>
       </c>
       <c r="H141" t="str">
-        <v>玉楮象谷関連資料</v>
+        <v>讃岐国絵図</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -13998,16 +14904,16 @@
         <v>歴史資料</v>
       </c>
       <c r="N141" t="str">
-        <v>高松市美術館</v>
+        <v>高松市歴史資料館</v>
       </c>
       <c r="O141" t="str">
-        <v>高松市紺屋町10-4</v>
+        <v>高松市昭和町一丁目2-20</v>
       </c>
       <c r="P141" t="str">
         <v/>
       </c>
       <c r="Q141" t="str">
-        <v>087-823-1711</v>
+        <v>087-861-4520</v>
       </c>
       <c r="R141" t="str">
         <v/>
@@ -14025,19 +14931,19 @@
         <v/>
       </c>
       <c r="W141" t="str">
-        <v>2012-03-01</v>
+        <v>2017-03-31</v>
       </c>
       <c r="X141" t="str">
         <v>火水木金土日</v>
       </c>
       <c r="Y141" t="str">
-        <v>09:30</v>
+        <v>09:00</v>
       </c>
       <c r="Z141" t="str">
         <v>17:00</v>
       </c>
       <c r="AA141" t="str">
-        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/7）利用不可</v>
+        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
       </c>
       <c r="AB141" t="str">
         <v/>
@@ -14058,7 +14964,7 @@
         <v/>
       </c>
       <c r="AH141" t="str">
-        <v>https://www.city.takamatsu.kagawa.jp/museum/takamatsu/</v>
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -14066,10 +14972,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="str">
-        <v>0</v>
+        <v>34.344189</v>
       </c>
       <c r="C142" t="str">
-        <v>0</v>
+        <v>134.034412</v>
       </c>
       <c r="D142" t="str">
         <v>37201</v>
@@ -14084,7 +14990,7 @@
         <v>高松市</v>
       </c>
       <c r="H142" t="str">
-        <v>水任流泳法</v>
+        <v>高松城天守鯱</v>
       </c>
       <c r="I142" t="str">
         <v/>
@@ -14096,22 +15002,22 @@
         <v/>
       </c>
       <c r="L142" t="str">
-        <v>市指定無形文化財</v>
+        <v>市指定有形文化財</v>
       </c>
       <c r="M142" t="str">
-        <v/>
+        <v>歴史資料</v>
       </c>
       <c r="N142" t="str">
-        <v/>
+        <v>高松市歴史資料館</v>
       </c>
       <c r="O142" t="str">
-        <v>高松市玉藻町</v>
+        <v>高松市昭和町一丁目2-20</v>
       </c>
       <c r="P142" t="str">
         <v/>
       </c>
       <c r="Q142" t="str">
-        <v/>
+        <v>087-861-4520</v>
       </c>
       <c r="R142" t="str">
         <v/>
@@ -14126,22 +15032,22 @@
         <v/>
       </c>
       <c r="V142" t="str">
-        <v>水任流保存会</v>
+        <v/>
       </c>
       <c r="W142" t="str">
-        <v>1979-11-27</v>
+        <v>2018-03-30</v>
       </c>
       <c r="X142" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y142" t="str">
-        <v/>
+        <v>09:00</v>
       </c>
       <c r="Z142" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA142" t="str">
-        <v/>
+        <v>（リニューアル工事のため令和９年秋頃まで休館中）入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/3）利用不可</v>
       </c>
       <c r="AB142" t="str">
         <v/>
@@ -14170,10 +15076,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="str">
-        <v>0</v>
+        <v>34.344347</v>
       </c>
       <c r="C143" t="str">
-        <v>0</v>
+        <v>134.049095</v>
       </c>
       <c r="D143" t="str">
         <v>37201</v>
@@ -14188,7 +15094,7 @@
         <v>高松市</v>
       </c>
       <c r="H143" t="str">
-        <v>清水神社の甕塚と上御盥跡</v>
+        <v>玉楮象谷関連資料</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -14200,22 +15106,22 @@
         <v/>
       </c>
       <c r="L143" t="str">
-        <v>市指定民俗文化財</v>
+        <v>市指定有形文化財</v>
       </c>
       <c r="M143" t="str">
-        <v>有形民俗</v>
+        <v>歴史資料</v>
       </c>
       <c r="N143" t="str">
-        <v>清水神社</v>
+        <v>高松市美術館</v>
       </c>
       <c r="O143" t="str">
-        <v>高松市由良町1050</v>
+        <v>高松市紺屋町10-4</v>
       </c>
       <c r="P143" t="str">
         <v/>
       </c>
       <c r="Q143" t="str">
-        <v/>
+        <v>087-823-1711</v>
       </c>
       <c r="R143" t="str">
         <v/>
@@ -14233,19 +15139,19 @@
         <v/>
       </c>
       <c r="W143" t="str">
-        <v>1981-09-10</v>
+        <v>2012-03-01</v>
       </c>
       <c r="X143" t="str">
-        <v/>
+        <v>火水木金土日</v>
       </c>
       <c r="Y143" t="str">
-        <v/>
+        <v>09:30</v>
       </c>
       <c r="Z143" t="str">
-        <v/>
+        <v>17:00</v>
       </c>
       <c r="AA143" t="str">
-        <v/>
+        <v>入館は16：30まで。月曜日（祝日の場合は翌平日）、年末年始（12/29～1/7）利用不可</v>
       </c>
       <c r="AB143" t="str">
         <v/>
@@ -14266,7 +15172,7 @@
         <v/>
       </c>
       <c r="AH143" t="str">
-        <v/>
+        <v>https://www.city.takamatsu.kagawa.jp/museum/takamatsu/</v>
       </c>
     </row>
     <row r="144">
@@ -14292,7 +15198,7 @@
         <v>高松市</v>
       </c>
       <c r="H144" t="str">
-        <v>住吉神社お船「住吉丸」（「弁才船」の模型）</v>
+        <v>水任流泳法</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -14304,16 +15210,16 @@
         <v/>
       </c>
       <c r="L144" t="str">
-        <v>市指定民俗文化財</v>
+        <v>市指定無形文化財</v>
       </c>
       <c r="M144" t="str">
-        <v>有形民俗</v>
+        <v/>
       </c>
       <c r="N144" t="str">
-        <v>住吉神社</v>
+        <v/>
       </c>
       <c r="O144" t="str">
-        <v>高松市庵治町鎌野5053</v>
+        <v>高松市玉藻町</v>
       </c>
       <c r="P144" t="str">
         <v/>
@@ -14334,10 +15240,10 @@
         <v/>
       </c>
       <c r="V144" t="str">
-        <v/>
+        <v>水任流保存会</v>
       </c>
       <c r="W144" t="str">
-        <v>1982-01-13</v>
+        <v>1979-11-27</v>
       </c>
       <c r="X144" t="str">
         <v/>
@@ -14396,7 +15302,7 @@
         <v>高松市</v>
       </c>
       <c r="H145" t="str">
-        <v>祇園座衣装</v>
+        <v>清水神社の甕塚と上御盥跡</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -14414,10 +15320,10 @@
         <v>有形民俗</v>
       </c>
       <c r="N145" t="str">
-        <v/>
+        <v>清水神社</v>
       </c>
       <c r="O145" t="str">
-        <v>高松市香川町東谷</v>
+        <v>高松市由良町1050</v>
       </c>
       <c r="P145" t="str">
         <v/>
@@ -14441,7 +15347,7 @@
         <v/>
       </c>
       <c r="W145" t="str">
-        <v>1986-03-31</v>
+        <v>1981-09-10</v>
       </c>
       <c r="X145" t="str">
         <v/>
@@ -14500,7 +15406,7 @@
         <v>高松市</v>
       </c>
       <c r="H146" t="str">
-        <v>才田獅子頭（額田喜左衛門作）</v>
+        <v>住吉神社お船「住吉丸」（「弁才船」の模型）</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -14518,10 +15424,10 @@
         <v>有形民俗</v>
       </c>
       <c r="N146" t="str">
-        <v/>
+        <v>住吉神社</v>
       </c>
       <c r="O146" t="str">
-        <v>高松市庵治町才田</v>
+        <v>高松市庵治町鎌野5053</v>
       </c>
       <c r="P146" t="str">
         <v/>
@@ -14545,7 +15451,7 @@
         <v/>
       </c>
       <c r="W146" t="str">
-        <v>2004-09-01</v>
+        <v>1982-01-13</v>
       </c>
       <c r="X146" t="str">
         <v/>
@@ -14604,7 +15510,7 @@
         <v>高松市</v>
       </c>
       <c r="H147" t="str">
-        <v>庵治おどり</v>
+        <v>祇園座衣装</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -14619,13 +15525,13 @@
         <v>市指定民俗文化財</v>
       </c>
       <c r="M147" t="str">
-        <v>無形民俗</v>
+        <v>有形民俗</v>
       </c>
       <c r="N147" t="str">
         <v/>
       </c>
       <c r="O147" t="str">
-        <v>高松市庵治町才田</v>
+        <v>高松市香川町東谷</v>
       </c>
       <c r="P147" t="str">
         <v/>
@@ -14649,7 +15555,7 @@
         <v/>
       </c>
       <c r="W147" t="str">
-        <v>1982-01-13</v>
+        <v>1986-03-31</v>
       </c>
       <c r="X147" t="str">
         <v/>
@@ -14708,7 +15614,7 @@
         <v>高松市</v>
       </c>
       <c r="H148" t="str">
-        <v>石切り唄</v>
+        <v>才田獅子頭（額田喜左衛門作）</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -14723,13 +15629,13 @@
         <v>市指定民俗文化財</v>
       </c>
       <c r="M148" t="str">
-        <v>無形民俗</v>
+        <v>有形民俗</v>
       </c>
       <c r="N148" t="str">
         <v/>
       </c>
       <c r="O148" t="str">
-        <v>高松市牟礼町牟礼</v>
+        <v>高松市庵治町才田</v>
       </c>
       <c r="P148" t="str">
         <v/>
@@ -14753,7 +15659,7 @@
         <v/>
       </c>
       <c r="W148" t="str">
-        <v>1982-04-01</v>
+        <v>2004-09-01</v>
       </c>
       <c r="X148" t="str">
         <v/>
@@ -14812,7 +15718,7 @@
         <v>高松市</v>
       </c>
       <c r="H149" t="str">
-        <v>田井の子供神相撲</v>
+        <v>庵治おどり</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -14833,7 +15739,7 @@
         <v/>
       </c>
       <c r="O149" t="str">
-        <v>高松市牟礼町牟礼</v>
+        <v>高松市庵治町才田</v>
       </c>
       <c r="P149" t="str">
         <v/>
@@ -14857,7 +15763,7 @@
         <v/>
       </c>
       <c r="W149" t="str">
-        <v>1982-04-01</v>
+        <v>1982-01-13</v>
       </c>
       <c r="X149" t="str">
         <v/>
@@ -14916,7 +15822,7 @@
         <v>高松市</v>
       </c>
       <c r="H150" t="str">
-        <v>ひょうげ祭り</v>
+        <v>石切り唄</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -14937,7 +15843,7 @@
         <v/>
       </c>
       <c r="O150" t="str">
-        <v>高松市香川町浅野</v>
+        <v>高松市牟礼町牟礼</v>
       </c>
       <c r="P150" t="str">
         <v/>
@@ -14961,7 +15867,7 @@
         <v/>
       </c>
       <c r="W150" t="str">
-        <v>1986-03-31</v>
+        <v>1982-04-01</v>
       </c>
       <c r="X150" t="str">
         <v/>
@@ -15020,7 +15926,7 @@
         <v>高松市</v>
       </c>
       <c r="H151" t="str">
-        <v>椛川たたら踊り</v>
+        <v>田井の子供神相撲</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -15041,7 +15947,7 @@
         <v/>
       </c>
       <c r="O151" t="str">
-        <v>高松市塩江町安原上東</v>
+        <v>高松市牟礼町牟礼</v>
       </c>
       <c r="P151" t="str">
         <v/>
@@ -15065,7 +15971,7 @@
         <v/>
       </c>
       <c r="W151" t="str">
-        <v>1997-08-26</v>
+        <v>1982-04-01</v>
       </c>
       <c r="X151" t="str">
         <v/>
@@ -15124,7 +16030,7 @@
         <v>高松市</v>
       </c>
       <c r="H152" t="str">
-        <v>庵治町才田岩陰獅子舞</v>
+        <v>ひょうげ祭り</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -15145,7 +16051,7 @@
         <v/>
       </c>
       <c r="O152" t="str">
-        <v>高松市庵治町才田</v>
+        <v>高松市香川町浅野</v>
       </c>
       <c r="P152" t="str">
         <v/>
@@ -15169,7 +16075,7 @@
         <v/>
       </c>
       <c r="W152" t="str">
-        <v>2006-01-04</v>
+        <v>1986-03-31</v>
       </c>
       <c r="X152" t="str">
         <v/>
@@ -15228,7 +16134,7 @@
         <v>高松市</v>
       </c>
       <c r="H153" t="str">
-        <v>石ヶ鼻古墳</v>
+        <v>椛川たたら踊り</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -15240,16 +16146,16 @@
         <v/>
       </c>
       <c r="L153" t="str">
-        <v>市指定記念物</v>
+        <v>市指定民俗文化財</v>
       </c>
       <c r="M153" t="str">
-        <v>史跡</v>
+        <v>無形民俗</v>
       </c>
       <c r="N153" t="str">
         <v/>
       </c>
       <c r="O153" t="str">
-        <v>高松市国分寺町福家</v>
+        <v>高松市塩江町安原上東</v>
       </c>
       <c r="P153" t="str">
         <v/>
@@ -15273,7 +16179,7 @@
         <v/>
       </c>
       <c r="W153" t="str">
-        <v>1970-03-28</v>
+        <v>1997-08-26</v>
       </c>
       <c r="X153" t="str">
         <v/>
@@ -15332,7 +16238,7 @@
         <v>高松市</v>
       </c>
       <c r="H154" t="str">
-        <v>久本古墳</v>
+        <v>庵治町才田岩陰獅子舞</v>
       </c>
       <c r="I154" t="str">
         <v/>
@@ -15344,16 +16250,16 @@
         <v/>
       </c>
       <c r="L154" t="str">
-        <v>市指定記念物</v>
+        <v>市指定民俗文化財</v>
       </c>
       <c r="M154" t="str">
-        <v>史跡</v>
+        <v>無形民俗</v>
       </c>
       <c r="N154" t="str">
         <v/>
       </c>
       <c r="O154" t="str">
-        <v>高松市新田町</v>
+        <v>高松市庵治町才田</v>
       </c>
       <c r="P154" t="str">
         <v/>
@@ -15377,7 +16283,7 @@
         <v/>
       </c>
       <c r="W154" t="str">
-        <v>1975-03-13</v>
+        <v>2006-01-04</v>
       </c>
       <c r="X154" t="str">
         <v/>
@@ -15436,7 +16342,7 @@
         <v>高松市</v>
       </c>
       <c r="H155" t="str">
-        <v>大井戸</v>
+        <v>石ヶ鼻古墳</v>
       </c>
       <c r="I155" t="str">
         <v/>
@@ -15457,7 +16363,7 @@
         <v/>
       </c>
       <c r="O155" t="str">
-        <v>高松市瓦町</v>
+        <v>高松市国分寺町福家</v>
       </c>
       <c r="P155" t="str">
         <v/>
@@ -15481,7 +16387,7 @@
         <v/>
       </c>
       <c r="W155" t="str">
-        <v>1975-10-23</v>
+        <v>1970-03-28</v>
       </c>
       <c r="X155" t="str">
         <v/>
@@ -15540,7 +16446,7 @@
         <v>高松市</v>
       </c>
       <c r="H156" t="str">
-        <v>前田城跡</v>
+        <v>久本古墳</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -15561,7 +16467,7 @@
         <v/>
       </c>
       <c r="O156" t="str">
-        <v>高松市前田西町</v>
+        <v>高松市新田町</v>
       </c>
       <c r="P156" t="str">
         <v/>
@@ -15585,7 +16491,7 @@
         <v/>
       </c>
       <c r="W156" t="str">
-        <v>1976-07-03</v>
+        <v>1975-03-13</v>
       </c>
       <c r="X156" t="str">
         <v/>
@@ -15644,7 +16550,7 @@
         <v>高松市</v>
       </c>
       <c r="H157" t="str">
-        <v>下司廃寺塔跡</v>
+        <v>大井戸</v>
       </c>
       <c r="I157" t="str">
         <v/>
@@ -15665,7 +16571,7 @@
         <v/>
       </c>
       <c r="O157" t="str">
-        <v>高松市東植田町</v>
+        <v>高松市瓦町</v>
       </c>
       <c r="P157" t="str">
         <v/>
@@ -15689,7 +16595,7 @@
         <v/>
       </c>
       <c r="W157" t="str">
-        <v>1976-07-03</v>
+        <v>1975-10-23</v>
       </c>
       <c r="X157" t="str">
         <v/>
@@ -15748,7 +16654,7 @@
         <v>高松市</v>
       </c>
       <c r="H158" t="str">
-        <v>藤尾城跡</v>
+        <v>前田城跡</v>
       </c>
       <c r="I158" t="str">
         <v/>
@@ -15766,10 +16672,10 @@
         <v>史跡</v>
       </c>
       <c r="N158" t="str">
-        <v>宇佐神社</v>
+        <v/>
       </c>
       <c r="O158" t="str">
-        <v>高松市香西本町465</v>
+        <v>高松市前田西町</v>
       </c>
       <c r="P158" t="str">
         <v/>
@@ -15852,7 +16758,7 @@
         <v>高松市</v>
       </c>
       <c r="H159" t="str">
-        <v>十河城跡</v>
+        <v>下司廃寺塔跡</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -15873,7 +16779,7 @@
         <v/>
       </c>
       <c r="O159" t="str">
-        <v>高松市十川東町</v>
+        <v>高松市東植田町</v>
       </c>
       <c r="P159" t="str">
         <v/>
@@ -15956,7 +16862,7 @@
         <v>高松市</v>
       </c>
       <c r="H160" t="str">
-        <v>東赤坂古墳</v>
+        <v>藤尾城跡</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -15974,10 +16880,10 @@
         <v>史跡</v>
       </c>
       <c r="N160" t="str">
-        <v/>
+        <v>宇佐神社</v>
       </c>
       <c r="O160" t="str">
-        <v>高松市香川町浅野</v>
+        <v>高松市香西本町465</v>
       </c>
       <c r="P160" t="str">
         <v/>
@@ -16001,7 +16907,7 @@
         <v/>
       </c>
       <c r="W160" t="str">
-        <v>1986-03-31</v>
+        <v>1976-07-03</v>
       </c>
       <c r="X160" t="str">
         <v/>
@@ -16060,7 +16966,7 @@
         <v>高松市</v>
       </c>
       <c r="H161" t="str">
-        <v>古宮古墳</v>
+        <v>十河城跡</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -16081,7 +16987,7 @@
         <v/>
       </c>
       <c r="O161" t="str">
-        <v>高松市鬼無町</v>
+        <v>高松市十川東町</v>
       </c>
       <c r="P161" t="str">
         <v/>
@@ -16105,7 +17011,7 @@
         <v/>
       </c>
       <c r="W161" t="str">
-        <v>1988-03-04</v>
+        <v>1976-07-03</v>
       </c>
       <c r="X161" t="str">
         <v/>
@@ -16164,7 +17070,7 @@
         <v>高松市</v>
       </c>
       <c r="H162" t="str">
-        <v>片山池１号窯跡</v>
+        <v>東赤坂古墳</v>
       </c>
       <c r="I162" t="str">
         <v/>
@@ -16185,7 +17091,7 @@
         <v/>
       </c>
       <c r="O162" t="str">
-        <v>高松市西春日町</v>
+        <v>高松市香川町浅野</v>
       </c>
       <c r="P162" t="str">
         <v/>
@@ -16209,7 +17115,7 @@
         <v/>
       </c>
       <c r="W162" t="str">
-        <v>1996-10-14</v>
+        <v>1986-03-31</v>
       </c>
       <c r="X162" t="str">
         <v/>
@@ -16268,7 +17174,7 @@
         <v>高松市</v>
       </c>
       <c r="H163" t="str">
-        <v>神内家墓地石塔群</v>
+        <v>古宮古墳</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -16289,7 +17195,7 @@
         <v/>
       </c>
       <c r="O163" t="str">
-        <v>高松市西植田町</v>
+        <v>高松市鬼無町</v>
       </c>
       <c r="P163" t="str">
         <v/>
@@ -16313,7 +17219,7 @@
         <v/>
       </c>
       <c r="W163" t="str">
-        <v>2005-05-10</v>
+        <v>1988-03-04</v>
       </c>
       <c r="X163" t="str">
         <v/>
@@ -16372,7 +17278,7 @@
         <v>高松市</v>
       </c>
       <c r="H164" t="str">
-        <v>横岡山古墳</v>
+        <v>片山池１号窯跡</v>
       </c>
       <c r="I164" t="str">
         <v/>
@@ -16393,7 +17299,7 @@
         <v/>
       </c>
       <c r="O164" t="str">
-        <v>高松市香川町浅野</v>
+        <v>高松市西春日町</v>
       </c>
       <c r="P164" t="str">
         <v/>
@@ -16417,7 +17323,7 @@
         <v/>
       </c>
       <c r="W164" t="str">
-        <v>2009-01-09</v>
+        <v>1996-10-14</v>
       </c>
       <c r="X164" t="str">
         <v/>
@@ -16476,7 +17382,7 @@
         <v>高松市</v>
       </c>
       <c r="H165" t="str">
-        <v>三谷石舟古墳</v>
+        <v>神内家墓地石塔群</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -16497,7 +17403,7 @@
         <v/>
       </c>
       <c r="O165" t="str">
-        <v>高松市三谷町</v>
+        <v>高松市西植田町</v>
       </c>
       <c r="P165" t="str">
         <v/>
@@ -16521,7 +17427,7 @@
         <v/>
       </c>
       <c r="W165" t="str">
-        <v>2014-03-10</v>
+        <v>2005-05-10</v>
       </c>
       <c r="X165" t="str">
         <v/>
@@ -16580,7 +17486,7 @@
         <v>高松市</v>
       </c>
       <c r="H166" t="str">
-        <v>大石さんのムクノキ</v>
+        <v>横岡山古墳</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -16595,13 +17501,13 @@
         <v>市指定記念物</v>
       </c>
       <c r="M166" t="str">
-        <v>天然記念物</v>
+        <v>史跡</v>
       </c>
       <c r="N166" t="str">
-        <v>天満神社</v>
+        <v/>
       </c>
       <c r="O166" t="str">
-        <v>高松市西山崎町1328-2</v>
+        <v>高松市香川町浅野</v>
       </c>
       <c r="P166" t="str">
         <v/>
@@ -16625,7 +17531,7 @@
         <v/>
       </c>
       <c r="W166" t="str">
-        <v>1975-03-13</v>
+        <v>2009-01-09</v>
       </c>
       <c r="X166" t="str">
         <v/>
@@ -16684,7 +17590,7 @@
         <v>高松市</v>
       </c>
       <c r="H167" t="str">
-        <v>男木島の柱状節理および岩海</v>
+        <v>三谷石舟古墳</v>
       </c>
       <c r="I167" t="str">
         <v/>
@@ -16699,13 +17605,13 @@
         <v>市指定記念物</v>
       </c>
       <c r="M167" t="str">
-        <v>天然記念物</v>
+        <v>史跡</v>
       </c>
       <c r="N167" t="str">
         <v/>
       </c>
       <c r="O167" t="str">
-        <v>高松市男木町</v>
+        <v>高松市三谷町</v>
       </c>
       <c r="P167" t="str">
         <v/>
@@ -16729,7 +17635,7 @@
         <v/>
       </c>
       <c r="W167" t="str">
-        <v>1976-07-03</v>
+        <v>2014-03-10</v>
       </c>
       <c r="X167" t="str">
         <v/>
@@ -16788,7 +17694,7 @@
         <v>高松市</v>
       </c>
       <c r="H168" t="str">
-        <v>女木島の柱状節理</v>
+        <v>大石さんのムクノキ</v>
       </c>
       <c r="I168" t="str">
         <v/>
@@ -16806,10 +17712,10 @@
         <v>天然記念物</v>
       </c>
       <c r="N168" t="str">
-        <v/>
+        <v>天満神社</v>
       </c>
       <c r="O168" t="str">
-        <v>高松市女木町</v>
+        <v>高松市西山崎町1328-2</v>
       </c>
       <c r="P168" t="str">
         <v/>
@@ -16833,7 +17739,7 @@
         <v/>
       </c>
       <c r="W168" t="str">
-        <v>1976-07-03</v>
+        <v>1975-03-13</v>
       </c>
       <c r="X168" t="str">
         <v/>
@@ -16892,7 +17798,7 @@
         <v>高松市</v>
       </c>
       <c r="H169" t="str">
-        <v>平石井神社のクロガネモチ</v>
+        <v>男木島の柱状節理および岩海</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -16910,10 +17816,10 @@
         <v>天然記念物</v>
       </c>
       <c r="N169" t="str">
-        <v>平石井神社</v>
+        <v/>
       </c>
       <c r="O169" t="str">
-        <v>高松市今里町2-1-10</v>
+        <v>高松市男木町</v>
       </c>
       <c r="P169" t="str">
         <v/>
@@ -16937,7 +17843,7 @@
         <v/>
       </c>
       <c r="W169" t="str">
-        <v>1979-08-01</v>
+        <v>1976-07-03</v>
       </c>
       <c r="X169" t="str">
         <v/>
@@ -16996,7 +17902,7 @@
         <v>高松市</v>
       </c>
       <c r="H170" t="str">
-        <v>如意輪寺のヤブツバキ</v>
+        <v>女木島の柱状節理</v>
       </c>
       <c r="I170" t="str">
         <v/>
@@ -17014,10 +17920,10 @@
         <v>天然記念物</v>
       </c>
       <c r="N170" t="str">
-        <v>如意輪寺</v>
+        <v/>
       </c>
       <c r="O170" t="str">
-        <v>高松市国分寺町国分2555</v>
+        <v>高松市女木町</v>
       </c>
       <c r="P170" t="str">
         <v/>
@@ -17041,7 +17947,7 @@
         <v/>
       </c>
       <c r="W170" t="str">
-        <v>1981-03-02</v>
+        <v>1976-07-03</v>
       </c>
       <c r="X170" t="str">
         <v/>
@@ -17100,7 +18006,7 @@
         <v>高松市</v>
       </c>
       <c r="H171" t="str">
-        <v>西方寺配水池のソメイヨシノ</v>
+        <v>平石井神社のクロガネモチ</v>
       </c>
       <c r="I171" t="str">
         <v/>
@@ -17118,10 +18024,10 @@
         <v>天然記念物</v>
       </c>
       <c r="N171" t="str">
-        <v>西方寺配水池</v>
+        <v>平石井神社</v>
       </c>
       <c r="O171" t="str">
-        <v>高松市西宝町三丁目738-1</v>
+        <v>高松市今里町2-1-10</v>
       </c>
       <c r="P171" t="str">
         <v/>
@@ -17145,7 +18051,7 @@
         <v/>
       </c>
       <c r="W171" t="str">
-        <v>2008-04-01</v>
+        <v>1979-08-01</v>
       </c>
       <c r="X171" t="str">
         <v/>
@@ -17204,7 +18110,7 @@
         <v>高松市</v>
       </c>
       <c r="H172" t="str">
-        <v>讃岐六条の水車及び関連用具</v>
+        <v>如意輪寺のヤブツバキ</v>
       </c>
       <c r="I172" t="str">
         <v/>
@@ -17216,16 +18122,16 @@
         <v/>
       </c>
       <c r="L172" t="str">
-        <v>国登録有形民俗文化財</v>
+        <v>市指定記念物</v>
       </c>
       <c r="M172" t="str">
-        <v>有形民俗</v>
+        <v>天然記念物</v>
       </c>
       <c r="N172" t="str">
-        <v/>
+        <v>如意輪寺</v>
       </c>
       <c r="O172" t="str">
-        <v>高松市六条町</v>
+        <v>高松市国分寺町国分2555</v>
       </c>
       <c r="P172" t="str">
         <v/>
@@ -17249,7 +18155,7 @@
         <v/>
       </c>
       <c r="W172" t="str">
-        <v>2016-03-02</v>
+        <v>1981-03-02</v>
       </c>
       <c r="X172" t="str">
         <v/>
@@ -17290,14 +18196,17 @@
         <v>172</v>
       </c>
       <c r="B173" t="str">
-        <v>34.284128</v>
+        <v>0</v>
       </c>
       <c r="C173" t="str">
-        <v>133.961514</v>
+        <v>0</v>
       </c>
       <c r="D173" t="str">
         <v>37201</v>
       </c>
+      <c r="E173" t="str">
+        <v/>
+      </c>
       <c r="F173" t="str">
         <v>香川県</v>
       </c>
@@ -17305,22 +18214,85 @@
         <v>高松市</v>
       </c>
       <c r="H173" t="str">
-        <v>文明塾扁額</v>
+        <v>西方寺配水池のソメイヨシノ</v>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
+      <c r="J173" t="str">
+        <v/>
+      </c>
+      <c r="K173" t="str">
+        <v/>
       </c>
       <c r="L173" t="str">
-        <v>市登録有形文化財</v>
+        <v>市指定記念物</v>
       </c>
       <c r="M173" t="str">
-        <v>歴史資料</v>
+        <v>天然記念物</v>
       </c>
       <c r="N173" t="str">
-        <v>国分寺南部小学校</v>
+        <v>西方寺配水池</v>
       </c>
       <c r="O173" t="str">
-        <v>高松市国分寺町福家甲3005</v>
+        <v>高松市西宝町三丁目738-1</v>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
+      <c r="R173" t="str">
+        <v/>
+      </c>
+      <c r="S173" t="str">
+        <v/>
+      </c>
+      <c r="T173" t="str">
+        <v/>
+      </c>
+      <c r="U173" t="str">
+        <v/>
+      </c>
+      <c r="V173" t="str">
+        <v/>
       </c>
       <c r="W173" t="str">
-        <v>2006-10-10</v>
+        <v>2008-04-01</v>
+      </c>
+      <c r="X173" t="str">
+        <v/>
+      </c>
+      <c r="Y173" t="str">
+        <v/>
+      </c>
+      <c r="Z173" t="str">
+        <v/>
+      </c>
+      <c r="AA173" t="str">
+        <v/>
+      </c>
+      <c r="AB173" t="str">
+        <v/>
+      </c>
+      <c r="AC173" t="str">
+        <v/>
+      </c>
+      <c r="AD173" t="str">
+        <v/>
+      </c>
+      <c r="AE173" t="str">
+        <v/>
+      </c>
+      <c r="AF173" t="str">
+        <v/>
+      </c>
+      <c r="AG173" t="str">
+        <v/>
+      </c>
+      <c r="AH173" t="str">
+        <v/>
       </c>
     </row>
     <row r="174">
@@ -17346,7 +18318,7 @@
         <v>高松市</v>
       </c>
       <c r="H174" t="str">
-        <v>城所山２号墳</v>
+        <v>讃岐六条の水車及び関連用具</v>
       </c>
       <c r="I174" t="str">
         <v/>
@@ -17358,16 +18330,16 @@
         <v/>
       </c>
       <c r="L174" t="str">
-        <v>市登録史跡</v>
+        <v>国登録有形民俗文化財</v>
       </c>
       <c r="M174" t="str">
-        <v>史跡</v>
+        <v>有形民俗</v>
       </c>
       <c r="N174" t="str">
         <v/>
       </c>
       <c r="O174" t="str">
-        <v>高松市香南町岡</v>
+        <v>高松市六条町</v>
       </c>
       <c r="P174" t="str">
         <v/>
@@ -17391,7 +18363,7 @@
         <v/>
       </c>
       <c r="W174" t="str">
-        <v>2006-10-10</v>
+        <v>2016-03-02</v>
       </c>
       <c r="X174" t="str">
         <v/>
@@ -17432,10 +18404,10 @@
         <v>174</v>
       </c>
       <c r="B175" t="str">
-        <v>0</v>
+        <v>34.284128</v>
       </c>
       <c r="C175" t="str">
-        <v>0</v>
+        <v>133.961514</v>
       </c>
       <c r="D175" t="str">
         <v>37201</v>
@@ -17450,7 +18422,7 @@
         <v>高松市</v>
       </c>
       <c r="H175" t="str">
-        <v>佐藤継信の墓</v>
+        <v>文明塾扁額</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -17462,16 +18434,16 @@
         <v/>
       </c>
       <c r="L175" t="str">
-        <v>市登録史跡</v>
+        <v>市登録有形文化財</v>
       </c>
       <c r="M175" t="str">
-        <v>史跡</v>
+        <v>歴史資料</v>
       </c>
       <c r="N175" t="str">
-        <v/>
+        <v>国分寺南部小学校</v>
       </c>
       <c r="O175" t="str">
-        <v>高松市牟礼町牟礼</v>
+        <v>高松市国分寺町福家甲3005</v>
       </c>
       <c r="P175" t="str">
         <v/>
@@ -17554,7 +18526,7 @@
         <v>高松市</v>
       </c>
       <c r="H176" t="str">
-        <v>総門</v>
+        <v>城所山２号墳</v>
       </c>
       <c r="I176" t="str">
         <v/>
@@ -17575,7 +18547,7 @@
         <v/>
       </c>
       <c r="O176" t="str">
-        <v>高松市牟礼町牟礼</v>
+        <v>高松市香南町岡</v>
       </c>
       <c r="P176" t="str">
         <v/>
@@ -17658,7 +18630,7 @@
         <v>高松市</v>
       </c>
       <c r="H177" t="str">
-        <v>射落畠</v>
+        <v>佐藤継信の墓</v>
       </c>
       <c r="I177" t="str">
         <v/>
@@ -17762,7 +18734,7 @@
         <v>高松市</v>
       </c>
       <c r="H178" t="str">
-        <v>祈り岩</v>
+        <v>総門</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -17866,7 +18838,7 @@
         <v>高松市</v>
       </c>
       <c r="H179" t="str">
-        <v>駒立岩</v>
+        <v>射落畠</v>
       </c>
       <c r="I179" t="str">
         <v/>
@@ -17970,7 +18942,7 @@
         <v>高松市</v>
       </c>
       <c r="H180" t="str">
-        <v>長刀泉</v>
+        <v>祈り岩</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -18074,7 +19046,7 @@
         <v>高松市</v>
       </c>
       <c r="H181" t="str">
-        <v>菜切地蔵</v>
+        <v>駒立岩</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -18178,7 +19150,7 @@
         <v>高松市</v>
       </c>
       <c r="H182" t="str">
-        <v>弁慶の投げ石</v>
+        <v>長刀泉</v>
       </c>
       <c r="I182" t="str">
         <v/>
@@ -18199,7 +19171,7 @@
         <v/>
       </c>
       <c r="O182" t="str">
-        <v>高松市牟礼町原</v>
+        <v>高松市牟礼町牟礼</v>
       </c>
       <c r="P182" t="str">
         <v/>
@@ -18282,7 +19254,7 @@
         <v>高松市</v>
       </c>
       <c r="H183" t="str">
-        <v>柴野栗山宅址</v>
+        <v>菜切地蔵</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -18300,10 +19272,10 @@
         <v>史跡</v>
       </c>
       <c r="N183" t="str">
-        <v>栗山記念館</v>
+        <v/>
       </c>
       <c r="O183" t="str">
-        <v>高松市牟礼町牟礼3028</v>
+        <v>高松市牟礼町牟礼</v>
       </c>
       <c r="P183" t="str">
         <v/>
@@ -18386,7 +19358,7 @@
         <v>高松市</v>
       </c>
       <c r="H184" t="str">
-        <v>六萬寺　附　杉の井</v>
+        <v>弁慶の投げ石</v>
       </c>
       <c r="I184" t="str">
         <v/>
@@ -18407,69 +19379,277 @@
         <v/>
       </c>
       <c r="O184" t="str">
+        <v>高松市牟礼町原</v>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
+      <c r="R184" t="str">
+        <v/>
+      </c>
+      <c r="S184" t="str">
+        <v/>
+      </c>
+      <c r="T184" t="str">
+        <v/>
+      </c>
+      <c r="U184" t="str">
+        <v/>
+      </c>
+      <c r="V184" t="str">
+        <v/>
+      </c>
+      <c r="W184" t="str">
+        <v>2006-10-10</v>
+      </c>
+      <c r="X184" t="str">
+        <v/>
+      </c>
+      <c r="Y184" t="str">
+        <v/>
+      </c>
+      <c r="Z184" t="str">
+        <v/>
+      </c>
+      <c r="AA184" t="str">
+        <v/>
+      </c>
+      <c r="AB184" t="str">
+        <v/>
+      </c>
+      <c r="AC184" t="str">
+        <v/>
+      </c>
+      <c r="AD184" t="str">
+        <v/>
+      </c>
+      <c r="AE184" t="str">
+        <v/>
+      </c>
+      <c r="AF184" t="str">
+        <v/>
+      </c>
+      <c r="AG184" t="str">
+        <v/>
+      </c>
+      <c r="AH184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>184</v>
+      </c>
+      <c r="B185" t="str">
+        <v>0</v>
+      </c>
+      <c r="C185" t="str">
+        <v>0</v>
+      </c>
+      <c r="D185" t="str">
+        <v>37201</v>
+      </c>
+      <c r="E185" t="str">
+        <v/>
+      </c>
+      <c r="F185" t="str">
+        <v>香川県</v>
+      </c>
+      <c r="G185" t="str">
+        <v>高松市</v>
+      </c>
+      <c r="H185" t="str">
+        <v>柴野栗山宅址</v>
+      </c>
+      <c r="I185" t="str">
+        <v/>
+      </c>
+      <c r="J185" t="str">
+        <v/>
+      </c>
+      <c r="K185" t="str">
+        <v/>
+      </c>
+      <c r="L185" t="str">
+        <v>市登録史跡</v>
+      </c>
+      <c r="M185" t="str">
+        <v>史跡</v>
+      </c>
+      <c r="N185" t="str">
+        <v>栗山記念館</v>
+      </c>
+      <c r="O185" t="str">
+        <v>高松市牟礼町牟礼3028</v>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
+      <c r="R185" t="str">
+        <v/>
+      </c>
+      <c r="S185" t="str">
+        <v/>
+      </c>
+      <c r="T185" t="str">
+        <v/>
+      </c>
+      <c r="U185" t="str">
+        <v/>
+      </c>
+      <c r="V185" t="str">
+        <v/>
+      </c>
+      <c r="W185" t="str">
+        <v>2006-10-10</v>
+      </c>
+      <c r="X185" t="str">
+        <v/>
+      </c>
+      <c r="Y185" t="str">
+        <v/>
+      </c>
+      <c r="Z185" t="str">
+        <v/>
+      </c>
+      <c r="AA185" t="str">
+        <v/>
+      </c>
+      <c r="AB185" t="str">
+        <v/>
+      </c>
+      <c r="AC185" t="str">
+        <v/>
+      </c>
+      <c r="AD185" t="str">
+        <v/>
+      </c>
+      <c r="AE185" t="str">
+        <v/>
+      </c>
+      <c r="AF185" t="str">
+        <v/>
+      </c>
+      <c r="AG185" t="str">
+        <v/>
+      </c>
+      <c r="AH185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>185</v>
+      </c>
+      <c r="B186" t="str">
+        <v>0</v>
+      </c>
+      <c r="C186" t="str">
+        <v>0</v>
+      </c>
+      <c r="D186" t="str">
+        <v>37201</v>
+      </c>
+      <c r="E186" t="str">
+        <v/>
+      </c>
+      <c r="F186" t="str">
+        <v>香川県</v>
+      </c>
+      <c r="G186" t="str">
+        <v>高松市</v>
+      </c>
+      <c r="H186" t="str">
+        <v>六萬寺　附　杉の井</v>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186" t="str">
+        <v/>
+      </c>
+      <c r="K186" t="str">
+        <v/>
+      </c>
+      <c r="L186" t="str">
+        <v>市登録史跡</v>
+      </c>
+      <c r="M186" t="str">
+        <v>史跡</v>
+      </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
         <v>高松市牟礼町牟礼</v>
       </c>
-      <c r="P184" t="str">
-        <v/>
-      </c>
-      <c r="Q184" t="str">
-        <v/>
-      </c>
-      <c r="R184" t="str">
-        <v/>
-      </c>
-      <c r="S184" t="str">
-        <v/>
-      </c>
-      <c r="T184" t="str">
-        <v/>
-      </c>
-      <c r="U184" t="str">
-        <v/>
-      </c>
-      <c r="V184" t="str">
-        <v/>
-      </c>
-      <c r="W184" t="str">
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
+      <c r="R186" t="str">
+        <v/>
+      </c>
+      <c r="S186" t="str">
+        <v/>
+      </c>
+      <c r="T186" t="str">
+        <v/>
+      </c>
+      <c r="U186" t="str">
+        <v/>
+      </c>
+      <c r="V186" t="str">
+        <v/>
+      </c>
+      <c r="W186" t="str">
         <v>2016-03-31</v>
       </c>
-      <c r="X184" t="str">
-        <v/>
-      </c>
-      <c r="Y184" t="str">
-        <v/>
-      </c>
-      <c r="Z184" t="str">
-        <v/>
-      </c>
-      <c r="AA184" t="str">
-        <v/>
-      </c>
-      <c r="AB184" t="str">
-        <v/>
-      </c>
-      <c r="AC184" t="str">
-        <v/>
-      </c>
-      <c r="AD184" t="str">
-        <v/>
-      </c>
-      <c r="AE184" t="str">
-        <v/>
-      </c>
-      <c r="AF184" t="str">
-        <v/>
-      </c>
-      <c r="AG184" t="str">
-        <v/>
-      </c>
-      <c r="AH184" t="str">
+      <c r="X186" t="str">
+        <v/>
+      </c>
+      <c r="Y186" t="str">
+        <v/>
+      </c>
+      <c r="Z186" t="str">
+        <v/>
+      </c>
+      <c r="AA186" t="str">
+        <v/>
+      </c>
+      <c r="AB186" t="str">
+        <v/>
+      </c>
+      <c r="AC186" t="str">
+        <v/>
+      </c>
+      <c r="AD186" t="str">
+        <v/>
+      </c>
+      <c r="AE186" t="str">
+        <v/>
+      </c>
+      <c r="AF186" t="str">
+        <v/>
+      </c>
+      <c r="AG186" t="str">
+        <v/>
+      </c>
+      <c r="AH186" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH184"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AH186"/>
   </ignoredErrors>
 </worksheet>
 </file>